--- a/data/processed/apartment_pricing_recommendations.xlsx
+++ b/data/processed/apartment_pricing_recommendations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,51 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>company_positioning_adjustment_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sales_phase_adjustment_pct</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>inventory_strategy_adjustment_pct</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>manual_adjustment_pct</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>manual_adjustment_amount</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>strategy_note</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>total_strategy_adjustment_pct</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>final_strategy_price</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>final_strategy_price_per_sqm</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
           <t>pricing_status</t>
         </is>
       </c>
@@ -660,7 +705,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4912343.838260072</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>69383.38754604621</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -763,7 +833,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4466900.325857485</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>68092.99277221777</v>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -866,7 +961,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3501004.232526614</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>61421.12688643183</v>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -965,7 +1085,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>4270577.861974038</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>61892.43278223243</v>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1068,7 +1213,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4279135.759502587</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>62016.46028264619</v>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1171,7 +1341,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4270551.626609786</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>61892.05255956212</v>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1274,7 +1469,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>6490421.747702251</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>58419.63769308957</v>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1377,7 +1597,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4474290.424801051</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>64844.78876523262</v>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1476,7 +1721,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4511972.320571836</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>65390.90319669327</v>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1579,7 +1849,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4504797.671148267</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65286.92277026473</v>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1682,7 +1977,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>6709778.606870472</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>60394.0468665209</v>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1781,7 +2101,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4669500.680397624</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>67673.9229043134</v>
+      </c>
+      <c r="AL13" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1880,7 +2225,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4678058.577926173</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>67797.95040472715</v>
+      </c>
+      <c r="AL14" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -1979,7 +2349,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>4669474.445033371</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>67673.54268164307</v>
+      </c>
+      <c r="AL15" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2082,7 +2477,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>6889344.566125836</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>62010.30212534506</v>
+      </c>
+      <c r="AL16" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2181,7 +2601,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>4873213.243224635</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>70626.27888731354</v>
+      </c>
+      <c r="AL17" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2284,7 +2729,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4910895.138995421</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>71172.39331877422</v>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2387,7 +2857,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4903720.489571851</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>71068.41289234566</v>
+      </c>
+      <c r="AL19" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2490,7 +2985,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>7108701.425294057</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>63984.7112987764</v>
+      </c>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2593,7 +3113,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>5068423.498821209</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>73455.41302639434</v>
+      </c>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2692,7 +3237,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>5076981.396349758</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>73579.44052680809</v>
+      </c>
+      <c r="AL22" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2795,7 +3365,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>5068397.263456956</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>73455.03280372401</v>
+      </c>
+      <c r="AL23" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -2898,7 +3493,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>7288267.384549422</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>65600.96655760056</v>
+      </c>
+      <c r="AL24" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3001,7 +3621,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>5272136.06164822</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>76407.76900939448</v>
+      </c>
+      <c r="AL25" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3100,7 +3745,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>5309817.957419006</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>76953.88344085516</v>
+      </c>
+      <c r="AL26" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3203,7 +3873,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>5302643.307995436</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>76849.9030144266</v>
+      </c>
+      <c r="AL27" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3306,7 +4001,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>7507624.243717643</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>67575.37573103189</v>
+      </c>
+      <c r="AL28" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3405,7 +4125,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>5467346.317244794</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>79236.90314847528</v>
+      </c>
+      <c r="AL29" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3504,7 +4249,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>5475904.214773343</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>79360.93064888903</v>
+      </c>
+      <c r="AL30" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3607,7 +4377,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>5467320.081880542</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>79236.52292580495</v>
+      </c>
+      <c r="AL31" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3710,7 +4505,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>7687190.202973006</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>69191.63098985604</v>
+      </c>
+      <c r="AL32" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3809,7 +4629,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>5671058.880071806</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>82189.25913147544</v>
+      </c>
+      <c r="AL33" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -3908,7 +4753,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>5708740.775842591</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>82735.3735629361</v>
+      </c>
+      <c r="AL34" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4007,7 +4877,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>5701566.126419021</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>82631.39313650756</v>
+      </c>
+      <c r="AL35" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4110,7 +5005,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>7906547.062141228</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>71166.04016328738</v>
+      </c>
+      <c r="AL36" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4213,7 +5133,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>15528580.96488991</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>60848.67149251532</v>
+      </c>
+      <c r="AL37" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4316,7 +5261,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>15781094.02076194</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>60673.17962615124</v>
+      </c>
+      <c r="AL38" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4419,7 +5389,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>11285398.3930051</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>66345.66956499177</v>
+      </c>
+      <c r="AL39" t="inlineStr">
         <is>
           <t>priced</t>
         </is>
@@ -4518,7 +5513,32 @@
           <t>synthetic_poc</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>10543870.66979108</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>66480.89955732079</v>
+      </c>
+      <c r="AL40" t="inlineStr">
         <is>
           <t>priced</t>
         </is>

--- a/data/processed/apartment_pricing_recommendations.xlsx
+++ b/data/processed/apartment_pricing_recommendations.xlsx
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3487207.670698496</v>
+        <v>4283519.560704757</v>
       </c>
       <c r="Q2" t="n">
-        <v>49254.34563133469</v>
+        <v>60501.68871051916</v>
       </c>
       <c r="R2" t="n">
         <v>8237661.562570418</v>
@@ -673,22 +673,22 @@
         <v>116351.1520137065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2441045.369488947</v>
+        <v>2141759.780352378</v>
       </c>
       <c r="W2" t="n">
-        <v>2471298.468771125</v>
+        <v>4118830.781285209</v>
       </c>
       <c r="X2" t="n">
-        <v>4912343.838260072</v>
+        <v>6260590.561637588</v>
       </c>
       <c r="Y2" t="n">
-        <v>69383.38754604621</v>
+        <v>88426.42036211283</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -706,13 +706,13 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -722,13 +722,13 @@
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4912343.838260072</v>
+        <v>6135378.750404836</v>
       </c>
       <c r="AK2" t="n">
-        <v>69383.38754604621</v>
+        <v>86657.89195487056</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3307049.333733289</v>
+        <v>3957301.615367981</v>
       </c>
       <c r="Q3" t="n">
-        <v>50412.33740447087</v>
+        <v>60324.71974646312</v>
       </c>
       <c r="R3" t="n">
         <v>7173219.307480612</v>
@@ -801,22 +801,22 @@
         <v>109347.8552969606</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V3" t="n">
-        <v>2314934.533613302</v>
+        <v>1978650.80768399</v>
       </c>
       <c r="W3" t="n">
-        <v>2151965.792244183</v>
+        <v>3586609.653740306</v>
       </c>
       <c r="X3" t="n">
-        <v>4466900.325857485</v>
+        <v>5565260.461424297</v>
       </c>
       <c r="Y3" t="n">
-        <v>68092.99277221777</v>
+        <v>84836.28752171184</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -850,13 +850,13 @@
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4466900.325857485</v>
+        <v>5453955.252195811</v>
       </c>
       <c r="AK3" t="n">
-        <v>68092.99277221777</v>
+        <v>83139.56177127761</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2839304.831580538</v>
+        <v>3395552.47607435</v>
       </c>
       <c r="Q4" t="n">
-        <v>49812.36546632523</v>
+        <v>59571.09607147983</v>
       </c>
       <c r="R4" t="n">
         <v>5044969.501400792</v>
@@ -929,22 +929,22 @@
         <v>88508.23686668056</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1987513.382106377</v>
+        <v>1697776.238037175</v>
       </c>
       <c r="W4" t="n">
-        <v>1513490.850420238</v>
+        <v>2522484.750700396</v>
       </c>
       <c r="X4" t="n">
-        <v>3501004.232526614</v>
+        <v>4220260.988737571</v>
       </c>
       <c r="Y4" t="n">
-        <v>61421.12688643183</v>
+        <v>74039.6664690802</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3501004.232526614</v>
+        <v>4135855.76896282</v>
       </c>
       <c r="AK4" t="n">
-        <v>61421.12688643183</v>
+        <v>72558.87313969858</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3702129.965534934</v>
+        <v>4337592.434186731</v>
       </c>
       <c r="Q5" t="n">
-        <v>53654.05747152078</v>
+        <v>62863.65846647437</v>
       </c>
       <c r="R5" t="n">
         <v>5596956.286998617</v>
@@ -1053,22 +1053,22 @@
         <v>81115.30850722632</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>2591490.975874453</v>
+        <v>2168796.217093366</v>
       </c>
       <c r="W5" t="n">
-        <v>1679086.886099585</v>
+        <v>2798478.143499308</v>
       </c>
       <c r="X5" t="n">
-        <v>4270577.861974038</v>
+        <v>4967274.360592674</v>
       </c>
       <c r="Y5" t="n">
-        <v>61892.43278223243</v>
+        <v>71989.48348685035</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1102,13 +1102,13 @@
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4270577.861974038</v>
+        <v>4867928.873380821</v>
       </c>
       <c r="AK5" t="n">
-        <v>61892.43278223243</v>
+        <v>70549.69381711335</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3702129.965534934</v>
+        <v>4337592.434186731</v>
       </c>
       <c r="Q6" t="n">
-        <v>53654.05747152078</v>
+        <v>62863.65846647437</v>
       </c>
       <c r="R6" t="n">
         <v>5625482.612093779</v>
@@ -1181,22 +1181,22 @@
         <v>81528.7335086055</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V6" t="n">
-        <v>2591490.975874453</v>
+        <v>2168796.217093366</v>
       </c>
       <c r="W6" t="n">
-        <v>1687644.783628134</v>
+        <v>2812741.30604689</v>
       </c>
       <c r="X6" t="n">
-        <v>4279135.759502587</v>
+        <v>4981537.523140255</v>
       </c>
       <c r="Y6" t="n">
-        <v>62016.46028264619</v>
+        <v>72196.19598753993</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1230,13 +1230,13 @@
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4279135.759502587</v>
+        <v>4881906.77267745</v>
       </c>
       <c r="AK6" t="n">
-        <v>62016.46028264619</v>
+        <v>70752.27206778913</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3702129.965534934</v>
+        <v>4337592.434186731</v>
       </c>
       <c r="Q7" t="n">
-        <v>53654.05747152078</v>
+        <v>62863.65846647437</v>
       </c>
       <c r="R7" t="n">
         <v>5596868.835784443</v>
@@ -1309,22 +1309,22 @@
         <v>81114.04109832525</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>2591490.975874453</v>
+        <v>2168796.217093366</v>
       </c>
       <c r="W7" t="n">
-        <v>1679060.650735333</v>
+        <v>2798434.417892221</v>
       </c>
       <c r="X7" t="n">
-        <v>4270551.626609786</v>
+        <v>4967230.634985587</v>
       </c>
       <c r="Y7" t="n">
-        <v>61892.05255956212</v>
+        <v>71988.8497823998</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4270551.626609786</v>
+        <v>4867886.022285875</v>
       </c>
       <c r="AK7" t="n">
-        <v>61892.05255956212</v>
+        <v>70549.07278675181</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5500300.237231525</v>
+        <v>7023172.797175091</v>
       </c>
       <c r="Q8" t="n">
-        <v>49507.65290037376</v>
+        <v>63214.87666224204</v>
       </c>
       <c r="R8" t="n">
         <v>8800705.272133948</v>
@@ -1437,22 +1437,22 @@
         <v>79214.26887609315</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>3850210.166062067</v>
+        <v>3511586.398587545</v>
       </c>
       <c r="W8" t="n">
-        <v>2640211.581640184</v>
+        <v>4400352.636066974</v>
       </c>
       <c r="X8" t="n">
-        <v>6490421.747702251</v>
+        <v>7911939.03465452</v>
       </c>
       <c r="Y8" t="n">
-        <v>58419.63769308957</v>
+        <v>71214.5727691676</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1486,13 +1486,13 @@
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6490421.747702251</v>
+        <v>7753700.253961429</v>
       </c>
       <c r="AK8" t="n">
-        <v>58419.63769308957</v>
+        <v>69790.28131378425</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3979414.761628558</v>
+        <v>4504586.904131437</v>
       </c>
       <c r="Q9" t="n">
-        <v>57672.67770476171</v>
+        <v>65283.86817581792</v>
       </c>
       <c r="R9" t="n">
         <v>5629000.305536865</v>
@@ -1565,22 +1565,22 @@
         <v>81579.71457299804</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V9" t="n">
-        <v>2785590.333139991</v>
+        <v>2252293.452065718</v>
       </c>
       <c r="W9" t="n">
-        <v>1688700.09166106</v>
+        <v>2814500.152768433</v>
       </c>
       <c r="X9" t="n">
-        <v>4474290.424801051</v>
+        <v>5066793.604834151</v>
       </c>
       <c r="Y9" t="n">
-        <v>64844.78876523262</v>
+        <v>73431.79137440799</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1614,13 +1614,13 @@
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4474290.424801051</v>
+        <v>4965457.732737468</v>
       </c>
       <c r="AK9" t="n">
-        <v>64844.78876523262</v>
+        <v>71963.15554691982</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3979414.761628558</v>
+        <v>4504586.904131437</v>
       </c>
       <c r="Q10" t="n">
-        <v>57672.67770476171</v>
+        <v>65283.86817581792</v>
       </c>
       <c r="R10" t="n">
         <v>5754606.624772819</v>
@@ -1689,22 +1689,22 @@
         <v>83400.09601120026</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V10" t="n">
-        <v>2785590.333139991</v>
+        <v>2252293.452065718</v>
       </c>
       <c r="W10" t="n">
-        <v>1726381.987431846</v>
+        <v>2877303.312386409</v>
       </c>
       <c r="X10" t="n">
-        <v>4511972.320571836</v>
+        <v>5129596.764452128</v>
       </c>
       <c r="Y10" t="n">
-        <v>65390.90319669327</v>
+        <v>74341.9820935091</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4511972.320571836</v>
+        <v>5027004.829163085</v>
       </c>
       <c r="AK10" t="n">
-        <v>65390.90319669327</v>
+        <v>72855.14245163891</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3979414.761628558</v>
+        <v>4504586.904131437</v>
       </c>
       <c r="Q11" t="n">
-        <v>57672.67770476171</v>
+        <v>65283.86817581792</v>
       </c>
       <c r="R11" t="n">
         <v>5730691.126694251</v>
@@ -1817,22 +1817,22 @@
         <v>83053.49458977176</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V11" t="n">
-        <v>2785590.333139991</v>
+        <v>2252293.452065718</v>
       </c>
       <c r="W11" t="n">
-        <v>1719207.338008275</v>
+        <v>2865345.563347125</v>
       </c>
       <c r="X11" t="n">
-        <v>4504797.671148267</v>
+        <v>5117639.015412844</v>
       </c>
       <c r="Y11" t="n">
-        <v>65286.92277026473</v>
+        <v>74168.68138279484</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1866,13 +1866,13 @@
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4504797.671148267</v>
+        <v>5015286.235104587</v>
       </c>
       <c r="AK11" t="n">
-        <v>65286.92277026473</v>
+        <v>72685.30775513894</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5777585.03332515</v>
+        <v>7190167.267119796</v>
       </c>
       <c r="Q12" t="n">
-        <v>52003.465646491</v>
+        <v>64717.97720179835</v>
       </c>
       <c r="R12" t="n">
         <v>8884896.945142893</v>
@@ -1945,22 +1945,22 @@
         <v>79972.06971325737</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V12" t="n">
-        <v>4044309.523327604</v>
+        <v>3595083.633559898</v>
       </c>
       <c r="W12" t="n">
-        <v>2665469.083542868</v>
+        <v>4442448.472571447</v>
       </c>
       <c r="X12" t="n">
-        <v>6709778.606870472</v>
+        <v>8037532.106131345</v>
       </c>
       <c r="Y12" t="n">
-        <v>60394.0468665209</v>
+        <v>72345.02345752786</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1994,13 +1994,13 @@
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ12" t="n">
-        <v>6709778.606870472</v>
+        <v>7876781.464008718</v>
       </c>
       <c r="AK12" t="n">
-        <v>60394.0468665209</v>
+        <v>70898.1229883773</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4256699.557722183</v>
+        <v>4671581.374076141</v>
       </c>
       <c r="Q13" t="n">
-        <v>61691.29793800265</v>
+        <v>67704.07788516146</v>
       </c>
       <c r="R13" t="n">
         <v>5632703.299973653</v>
@@ -2069,22 +2069,22 @@
         <v>81633.38115903844</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V13" t="n">
-        <v>2979689.690405528</v>
+        <v>2335790.687038071</v>
       </c>
       <c r="W13" t="n">
-        <v>1689810.989992096</v>
+        <v>2816351.649986826</v>
       </c>
       <c r="X13" t="n">
-        <v>4669500.680397624</v>
+        <v>5152142.337024897</v>
       </c>
       <c r="Y13" t="n">
-        <v>67673.9229043134</v>
+        <v>74668.72952209997</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2118,13 +2118,13 @@
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4669500.680397624</v>
+        <v>5049099.490284399</v>
       </c>
       <c r="AK13" t="n">
-        <v>67673.9229043134</v>
+        <v>73175.35493165796</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4256699.557722183</v>
+        <v>4671581.374076141</v>
       </c>
       <c r="Q14" t="n">
-        <v>61691.29793800265</v>
+        <v>67704.07788516146</v>
       </c>
       <c r="R14" t="n">
         <v>5661229.625068815</v>
@@ -2193,22 +2193,22 @@
         <v>82046.80616041762</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V14" t="n">
-        <v>2979689.690405528</v>
+        <v>2335790.687038071</v>
       </c>
       <c r="W14" t="n">
-        <v>1698368.887520645</v>
+        <v>2830614.812534408</v>
       </c>
       <c r="X14" t="n">
-        <v>4678058.577926173</v>
+        <v>5166405.499572478</v>
       </c>
       <c r="Y14" t="n">
-        <v>67797.95040472715</v>
+        <v>74875.44202278955</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2226,13 +2226,13 @@
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2242,13 +2242,13 @@
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4678058.577926173</v>
+        <v>5063077.389581028</v>
       </c>
       <c r="AK14" t="n">
-        <v>67797.95040472715</v>
+        <v>73377.93318233374</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4256699.557722183</v>
+        <v>4671581.374076141</v>
       </c>
       <c r="Q15" t="n">
-        <v>61691.29793800265</v>
+        <v>67704.07788516146</v>
       </c>
       <c r="R15" t="n">
         <v>5632615.848759479</v>
@@ -2317,22 +2317,22 @@
         <v>81632.11375013737</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>2979689.690405528</v>
+        <v>2335790.687038071</v>
       </c>
       <c r="W15" t="n">
-        <v>1689784.754627844</v>
+        <v>2816307.924379739</v>
       </c>
       <c r="X15" t="n">
-        <v>4669474.445033371</v>
+        <v>5152098.61141781</v>
       </c>
       <c r="Y15" t="n">
-        <v>67673.54268164307</v>
+        <v>74668.09581764942</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2366,13 +2366,13 @@
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4669474.445033371</v>
+        <v>5049056.639189453</v>
       </c>
       <c r="AK15" t="n">
-        <v>67673.54268164307</v>
+        <v>73174.73390129642</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>6054869.829418774</v>
+        <v>7357161.7370645</v>
       </c>
       <c r="Q16" t="n">
-        <v>54499.27839260823</v>
+        <v>66221.07774135465</v>
       </c>
       <c r="R16" t="n">
         <v>8836452.285108984</v>
@@ -2445,22 +2445,22 @@
         <v>79536.02416839769</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="n">
-        <v>4238408.880593142</v>
+        <v>3678580.86853225</v>
       </c>
       <c r="W16" t="n">
-        <v>2650935.685532695</v>
+        <v>4418226.142554492</v>
       </c>
       <c r="X16" t="n">
-        <v>6889344.566125836</v>
+        <v>8096807.011086741</v>
       </c>
       <c r="Y16" t="n">
-        <v>62010.30212534506</v>
+        <v>72878.55095487616</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ16" t="n">
-        <v>6889344.566125836</v>
+        <v>7934870.870865007</v>
       </c>
       <c r="AK16" t="n">
-        <v>62010.30212534506</v>
+        <v>71420.97993577864</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4533984.353815807</v>
+        <v>4838575.844020846</v>
       </c>
       <c r="Q17" t="n">
-        <v>65709.91817124358</v>
+        <v>70124.28759450502</v>
       </c>
       <c r="R17" t="n">
         <v>5664747.318511901</v>
@@ -2569,22 +2569,22 @@
         <v>82097.78722481016</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V17" t="n">
-        <v>3173789.047671065</v>
+        <v>2419287.922010423</v>
       </c>
       <c r="W17" t="n">
-        <v>1699424.19555357</v>
+        <v>2832373.659255951</v>
       </c>
       <c r="X17" t="n">
-        <v>4873213.243224635</v>
+        <v>5251661.581266373</v>
       </c>
       <c r="Y17" t="n">
-        <v>70626.27888731354</v>
+        <v>76111.03740965758</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2618,13 +2618,13 @@
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4873213.243224635</v>
+        <v>5146628.349641046</v>
       </c>
       <c r="AK17" t="n">
-        <v>70626.27888731354</v>
+        <v>74588.81666146443</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4533984.353815807</v>
+        <v>4838575.844020846</v>
       </c>
       <c r="Q18" t="n">
-        <v>65709.91817124358</v>
+        <v>70124.28759450502</v>
       </c>
       <c r="R18" t="n">
         <v>5790353.637747855</v>
@@ -2697,22 +2697,22 @@
         <v>83918.16866301239</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V18" t="n">
-        <v>3173789.047671065</v>
+        <v>2419287.922010423</v>
       </c>
       <c r="W18" t="n">
-        <v>1737106.091324356</v>
+        <v>2895176.818873927</v>
       </c>
       <c r="X18" t="n">
-        <v>4910895.138995421</v>
+        <v>5314464.740884351</v>
       </c>
       <c r="Y18" t="n">
-        <v>71172.39331877422</v>
+        <v>77021.22812875871</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2746,13 +2746,13 @@
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4910895.138995421</v>
+        <v>5208175.446066664</v>
       </c>
       <c r="AK18" t="n">
-        <v>71172.39331877422</v>
+        <v>75480.80356618353</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4533984.353815807</v>
+        <v>4838575.844020846</v>
       </c>
       <c r="Q19" t="n">
-        <v>65709.91817124358</v>
+        <v>70124.28759450502</v>
       </c>
       <c r="R19" t="n">
         <v>5766438.139669287</v>
@@ -2825,22 +2825,22 @@
         <v>83571.56724158386</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V19" t="n">
-        <v>3173789.047671065</v>
+        <v>2419287.922010423</v>
       </c>
       <c r="W19" t="n">
-        <v>1729931.441900786</v>
+        <v>2883219.069834644</v>
       </c>
       <c r="X19" t="n">
-        <v>4903720.489571851</v>
+        <v>5302506.991845067</v>
       </c>
       <c r="Y19" t="n">
-        <v>71068.41289234566</v>
+        <v>76847.92741804445</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2874,13 +2874,13 @@
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4903720.489571851</v>
+        <v>5196456.852008165</v>
       </c>
       <c r="AK19" t="n">
-        <v>71068.41289234566</v>
+        <v>75310.96886968355</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>6332154.625512399</v>
+        <v>7524156.207009205</v>
       </c>
       <c r="Q20" t="n">
-        <v>56995.09113872547</v>
+        <v>67724.17828091094</v>
       </c>
       <c r="R20" t="n">
         <v>8920643.958117928</v>
@@ -2953,22 +2953,22 @@
         <v>80293.82500556191</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V20" t="n">
-        <v>4432508.237858679</v>
+        <v>3762078.103504602</v>
       </c>
       <c r="W20" t="n">
-        <v>2676193.187435378</v>
+        <v>4460321.979058964</v>
       </c>
       <c r="X20" t="n">
-        <v>7108701.425294057</v>
+        <v>8222400.082563566</v>
       </c>
       <c r="Y20" t="n">
-        <v>63984.7112987764</v>
+        <v>74009.00164323642</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3002,13 +3002,13 @@
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7108701.425294057</v>
+        <v>8057952.080912295</v>
       </c>
       <c r="AK20" t="n">
-        <v>63984.7112987764</v>
+        <v>72528.8216103717</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4811269.149909432</v>
+        <v>5005570.313965551</v>
       </c>
       <c r="Q21" t="n">
-        <v>69728.53840448453</v>
+        <v>72544.49730384856</v>
       </c>
       <c r="R21" t="n">
         <v>5668450.312948689</v>
@@ -3081,22 +3081,22 @@
         <v>82151.45381085057</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V21" t="n">
-        <v>3367888.404936602</v>
+        <v>2502785.156982775</v>
       </c>
       <c r="W21" t="n">
-        <v>1700535.093884607</v>
+        <v>2834225.156474344</v>
       </c>
       <c r="X21" t="n">
-        <v>5068423.498821209</v>
+        <v>5337010.31345712</v>
       </c>
       <c r="Y21" t="n">
-        <v>73455.41302639434</v>
+        <v>77347.97555734956</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -3114,13 +3114,13 @@
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3130,13 +3130,13 @@
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5068423.498821209</v>
+        <v>5230270.107187978</v>
       </c>
       <c r="AK21" t="n">
-        <v>73455.41302639434</v>
+        <v>75801.01604620258</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4811269.149909432</v>
+        <v>5005570.313965551</v>
       </c>
       <c r="Q22" t="n">
-        <v>69728.53840448453</v>
+        <v>72544.49730384856</v>
       </c>
       <c r="R22" t="n">
         <v>5696976.638043852</v>
@@ -3205,22 +3205,22 @@
         <v>82564.87881222973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V22" t="n">
-        <v>3367888.404936602</v>
+        <v>2502785.156982775</v>
       </c>
       <c r="W22" t="n">
-        <v>1709092.991413155</v>
+        <v>2848488.319021926</v>
       </c>
       <c r="X22" t="n">
-        <v>5076981.396349758</v>
+        <v>5351273.476004701</v>
       </c>
       <c r="Y22" t="n">
-        <v>73579.44052680809</v>
+        <v>77554.68805803914</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3254,13 +3254,13 @@
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5076981.396349758</v>
+        <v>5244248.006484607</v>
       </c>
       <c r="AK22" t="n">
-        <v>73579.44052680809</v>
+        <v>76003.59429687836</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4811269.149909432</v>
+        <v>5005570.313965551</v>
       </c>
       <c r="Q23" t="n">
-        <v>69728.53840448453</v>
+        <v>72544.49730384856</v>
       </c>
       <c r="R23" t="n">
         <v>5668362.861734515</v>
@@ -3333,22 +3333,22 @@
         <v>82150.1864019495</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V23" t="n">
-        <v>3367888.404936602</v>
+        <v>2502785.156982775</v>
       </c>
       <c r="W23" t="n">
-        <v>1700508.858520354</v>
+        <v>2834181.430867258</v>
       </c>
       <c r="X23" t="n">
-        <v>5068397.263456956</v>
+        <v>5336966.587850032</v>
       </c>
       <c r="Y23" t="n">
-        <v>73455.03280372401</v>
+        <v>77347.34185289902</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3382,13 +3382,13 @@
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5068397.263456956</v>
+        <v>5230227.256093032</v>
       </c>
       <c r="AK23" t="n">
-        <v>73455.03280372401</v>
+        <v>75800.39501584104</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6609439.421606023</v>
+        <v>7691150.67695391</v>
       </c>
       <c r="Q24" t="n">
-        <v>59490.90388484269</v>
+        <v>69227.27882046724</v>
       </c>
       <c r="R24" t="n">
         <v>8872199.298084021</v>
@@ -3461,22 +3461,22 @@
         <v>79857.77946070227</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V24" t="n">
-        <v>4626607.595124216</v>
+        <v>3845575.338476955</v>
       </c>
       <c r="W24" t="n">
-        <v>2661659.789425206</v>
+        <v>4436099.64904201</v>
       </c>
       <c r="X24" t="n">
-        <v>7288267.384549422</v>
+        <v>8281674.987518965</v>
       </c>
       <c r="Y24" t="n">
-        <v>65600.96655760056</v>
+        <v>74542.52914058475</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3510,13 +3510,13 @@
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7288267.384549422</v>
+        <v>8116041.487768586</v>
       </c>
       <c r="AK24" t="n">
-        <v>65600.96655760056</v>
+        <v>73051.67855777305</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>5088553.946003056</v>
+        <v>5172564.783910255</v>
       </c>
       <c r="Q25" t="n">
-        <v>73747.15863772546</v>
+        <v>74964.70701319211</v>
       </c>
       <c r="R25" t="n">
         <v>5700494.331486938</v>
@@ -3589,22 +3589,22 @@
         <v>82615.85987662229</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V25" t="n">
-        <v>3561987.762202139</v>
+        <v>2586282.391955127</v>
       </c>
       <c r="W25" t="n">
-        <v>1710148.299446081</v>
+        <v>2850247.165743469</v>
       </c>
       <c r="X25" t="n">
-        <v>5272136.06164822</v>
+        <v>5436529.557698596</v>
       </c>
       <c r="Y25" t="n">
-        <v>76407.76900939448</v>
+        <v>78790.2834449072</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3638,13 +3638,13 @@
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5272136.06164822</v>
+        <v>5327798.966544624</v>
       </c>
       <c r="AK25" t="n">
-        <v>76407.76900939448</v>
+        <v>77214.47777600905</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>5088553.946003056</v>
+        <v>5172564.783910255</v>
       </c>
       <c r="Q26" t="n">
-        <v>73747.15863772546</v>
+        <v>74964.70701319211</v>
       </c>
       <c r="R26" t="n">
         <v>5826100.650722891</v>
@@ -3713,22 +3713,22 @@
         <v>84436.24131482451</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V26" t="n">
-        <v>3561987.762202139</v>
+        <v>2586282.391955127</v>
       </c>
       <c r="W26" t="n">
-        <v>1747830.195216867</v>
+        <v>2913050.325361446</v>
       </c>
       <c r="X26" t="n">
-        <v>5309817.957419006</v>
+        <v>5499332.717316573</v>
       </c>
       <c r="Y26" t="n">
-        <v>76953.88344085516</v>
+        <v>79700.47416400831</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3762,13 +3762,13 @@
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ26" t="n">
-        <v>5309817.957419006</v>
+        <v>5389346.062970242</v>
       </c>
       <c r="AK26" t="n">
-        <v>76953.88344085516</v>
+        <v>78106.46468072814</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>5088553.946003056</v>
+        <v>5172564.783910255</v>
       </c>
       <c r="Q27" t="n">
-        <v>73747.15863772546</v>
+        <v>74964.70701319211</v>
       </c>
       <c r="R27" t="n">
         <v>5802185.152644323</v>
@@ -3841,22 +3841,22 @@
         <v>84089.63989339599</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>3561987.762202139</v>
+        <v>2586282.391955127</v>
       </c>
       <c r="W27" t="n">
-        <v>1740655.545793297</v>
+        <v>2901092.576322162</v>
       </c>
       <c r="X27" t="n">
-        <v>5302643.307995436</v>
+        <v>5487374.968277289</v>
       </c>
       <c r="Y27" t="n">
-        <v>76849.9030144266</v>
+        <v>79527.17345329403</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3874,13 +3874,13 @@
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5302643.307995436</v>
+        <v>5377627.468911743</v>
       </c>
       <c r="AK27" t="n">
-        <v>76849.9030144266</v>
+        <v>77936.62998422816</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>6886724.217699647</v>
+        <v>7858145.146898614</v>
       </c>
       <c r="Q28" t="n">
-        <v>61986.71663095992</v>
+        <v>70730.37936002354</v>
       </c>
       <c r="R28" t="n">
         <v>8956390.971092965</v>
@@ -3969,22 +3969,22 @@
         <v>80615.58029786649</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V28" t="n">
-        <v>4820706.952389752</v>
+        <v>3929072.573449307</v>
       </c>
       <c r="W28" t="n">
-        <v>2686917.29132789</v>
+        <v>4478195.485546483</v>
       </c>
       <c r="X28" t="n">
-        <v>7507624.243717643</v>
+        <v>8407268.058995791</v>
       </c>
       <c r="Y28" t="n">
-        <v>67575.37573103189</v>
+        <v>75672.97982894501</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -4002,13 +4002,13 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4018,13 +4018,13 @@
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7507624.243717643</v>
+        <v>8239122.697815875</v>
       </c>
       <c r="AK28" t="n">
-        <v>67575.37573103189</v>
+        <v>74159.52023236611</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5365838.742096681</v>
+        <v>5339559.253854959</v>
       </c>
       <c r="Q29" t="n">
-        <v>77765.77887096639</v>
+        <v>77384.91672253564</v>
       </c>
       <c r="R29" t="n">
         <v>5704197.325923725</v>
@@ -4093,22 +4093,22 @@
         <v>82669.52646266269</v>
       </c>
       <c r="T29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V29" t="n">
-        <v>3756087.119467677</v>
+        <v>2669779.62692748</v>
       </c>
       <c r="W29" t="n">
-        <v>1711259.197777117</v>
+        <v>2852098.662961863</v>
       </c>
       <c r="X29" t="n">
-        <v>5467346.317244794</v>
+        <v>5521878.289889342</v>
       </c>
       <c r="Y29" t="n">
-        <v>79236.90314847528</v>
+        <v>80027.22159259916</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4142,13 +4142,13 @@
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ29" t="n">
-        <v>5467346.317244794</v>
+        <v>5411440.724091555</v>
       </c>
       <c r="AK29" t="n">
-        <v>79236.90314847528</v>
+        <v>78426.67716074717</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5365838.742096681</v>
+        <v>5339559.253854959</v>
       </c>
       <c r="Q30" t="n">
-        <v>77765.77887096639</v>
+        <v>77384.91672253564</v>
       </c>
       <c r="R30" t="n">
         <v>5732723.651018888</v>
@@ -4217,22 +4217,22 @@
         <v>83082.95146404185</v>
       </c>
       <c r="T30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V30" t="n">
-        <v>3756087.119467677</v>
+        <v>2669779.62692748</v>
       </c>
       <c r="W30" t="n">
-        <v>1719817.095305666</v>
+        <v>2866361.825509444</v>
       </c>
       <c r="X30" t="n">
-        <v>5475904.214773343</v>
+        <v>5536141.452436924</v>
       </c>
       <c r="Y30" t="n">
-        <v>79360.93064888903</v>
+        <v>80233.93409328876</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4266,13 +4266,13 @@
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ30" t="n">
-        <v>5475904.214773343</v>
+        <v>5425418.623388185</v>
       </c>
       <c r="AK30" t="n">
-        <v>79360.93064888903</v>
+        <v>78629.25541142297</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5365838.742096681</v>
+        <v>5339559.253854959</v>
       </c>
       <c r="Q31" t="n">
-        <v>77765.77887096639</v>
+        <v>77384.91672253564</v>
       </c>
       <c r="R31" t="n">
         <v>5704109.874709551</v>
@@ -4345,22 +4345,22 @@
         <v>82668.25905376161</v>
       </c>
       <c r="T31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V31" t="n">
-        <v>3756087.119467677</v>
+        <v>2669779.62692748</v>
       </c>
       <c r="W31" t="n">
-        <v>1711232.962412865</v>
+        <v>2852054.937354776</v>
       </c>
       <c r="X31" t="n">
-        <v>5467320.081880542</v>
+        <v>5521834.564282255</v>
       </c>
       <c r="Y31" t="n">
-        <v>79236.52292580495</v>
+        <v>80026.58788814863</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4394,13 +4394,13 @@
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5467320.081880542</v>
+        <v>5411397.87299661</v>
       </c>
       <c r="AK31" t="n">
-        <v>79236.52292580495</v>
+        <v>78426.05613038565</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7164009.013793272</v>
+        <v>8025139.616843319</v>
       </c>
       <c r="Q32" t="n">
-        <v>64482.52937707716</v>
+        <v>72233.47989957983</v>
       </c>
       <c r="R32" t="n">
         <v>8907946.311059056</v>
@@ -4473,22 +4473,22 @@
         <v>80179.53475300681</v>
       </c>
       <c r="T32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V32" t="n">
-        <v>5014806.30965529</v>
+        <v>4012569.808421659</v>
       </c>
       <c r="W32" t="n">
-        <v>2672383.893317717</v>
+        <v>4453973.155529528</v>
       </c>
       <c r="X32" t="n">
-        <v>7687190.202973006</v>
+        <v>8466542.963951187</v>
       </c>
       <c r="Y32" t="n">
-        <v>69191.63098985604</v>
+        <v>76206.50732629331</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4522,13 +4522,13 @@
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ32" t="n">
-        <v>7687190.202973006</v>
+        <v>8297212.104672164</v>
       </c>
       <c r="AK32" t="n">
-        <v>69191.63098985604</v>
+        <v>74682.37717976746</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5643123.538190305</v>
+        <v>5506553.723799665</v>
       </c>
       <c r="Q33" t="n">
-        <v>81784.39910420732</v>
+        <v>79805.12643187919</v>
       </c>
       <c r="R33" t="n">
         <v>5736241.344461974</v>
@@ -4597,22 +4597,22 @@
         <v>83133.93252843441</v>
       </c>
       <c r="T33" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V33" t="n">
-        <v>3950186.476733213</v>
+        <v>2753276.861899832</v>
       </c>
       <c r="W33" t="n">
-        <v>1720872.403338592</v>
+        <v>2868120.672230987</v>
       </c>
       <c r="X33" t="n">
-        <v>5671058.880071806</v>
+        <v>5621397.534130819</v>
       </c>
       <c r="Y33" t="n">
-        <v>82189.25913147544</v>
+        <v>81469.52948015679</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4646,13 +4646,13 @@
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ33" t="n">
-        <v>5671058.880071806</v>
+        <v>5508969.583448202</v>
       </c>
       <c r="AK33" t="n">
-        <v>82189.25913147544</v>
+        <v>79840.13889055366</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5643123.538190305</v>
+        <v>5506553.723799665</v>
       </c>
       <c r="Q34" t="n">
-        <v>81784.39910420732</v>
+        <v>79805.12643187919</v>
       </c>
       <c r="R34" t="n">
         <v>5861847.663697927</v>
@@ -4721,22 +4721,22 @@
         <v>84954.31396663663</v>
       </c>
       <c r="T34" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V34" t="n">
-        <v>3950186.476733213</v>
+        <v>2753276.861899832</v>
       </c>
       <c r="W34" t="n">
-        <v>1758554.299109378</v>
+        <v>2930923.831848964</v>
       </c>
       <c r="X34" t="n">
-        <v>5708740.775842591</v>
+        <v>5684200.693748796</v>
       </c>
       <c r="Y34" t="n">
-        <v>82735.3735629361</v>
+        <v>82379.72019925792</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4754,13 +4754,13 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4770,13 +4770,13 @@
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ34" t="n">
-        <v>5708740.775842591</v>
+        <v>5570516.67987382</v>
       </c>
       <c r="AK34" t="n">
-        <v>82735.3735629361</v>
+        <v>80732.12579527276</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5643123.538190305</v>
+        <v>5506553.723799665</v>
       </c>
       <c r="Q35" t="n">
-        <v>81784.39910420732</v>
+        <v>79805.12643187919</v>
       </c>
       <c r="R35" t="n">
         <v>5837932.165619359</v>
@@ -4845,22 +4845,22 @@
         <v>84607.71254520811</v>
       </c>
       <c r="T35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V35" t="n">
-        <v>3950186.476733213</v>
+        <v>2753276.861899832</v>
       </c>
       <c r="W35" t="n">
-        <v>1751379.649685808</v>
+        <v>2918966.08280968</v>
       </c>
       <c r="X35" t="n">
-        <v>5701566.126419021</v>
+        <v>5672242.944709511</v>
       </c>
       <c r="Y35" t="n">
-        <v>82631.39313650756</v>
+        <v>82206.41948854364</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4878,13 +4878,13 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4894,13 +4894,13 @@
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5701566.126419021</v>
+        <v>5558798.085815321</v>
       </c>
       <c r="AK35" t="n">
-        <v>82631.39313650756</v>
+        <v>80562.29109877277</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7441293.809886897</v>
+        <v>8192134.086788024</v>
       </c>
       <c r="Q36" t="n">
-        <v>66978.34212319439</v>
+        <v>73736.58043913613</v>
       </c>
       <c r="R36" t="n">
         <v>8992137.984068001</v>
@@ -4973,22 +4973,22 @@
         <v>80937.33559017103</v>
       </c>
       <c r="T36" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V36" t="n">
-        <v>5208905.666920828</v>
+        <v>4096067.043394012</v>
       </c>
       <c r="W36" t="n">
-        <v>2697641.3952204</v>
+        <v>4496068.992034</v>
       </c>
       <c r="X36" t="n">
-        <v>7906547.062141228</v>
+        <v>8592136.035428012</v>
       </c>
       <c r="Y36" t="n">
-        <v>71166.04016328738</v>
+        <v>77336.95801465357</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ36" t="n">
-        <v>7906547.062141228</v>
+        <v>8420293.314719452</v>
       </c>
       <c r="AK36" t="n">
-        <v>71166.04016328738</v>
+        <v>75790.2188543605</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>12880833.6194382</v>
+        <v>17421364.54085964</v>
       </c>
       <c r="Q37" t="n">
-        <v>50473.48596958544</v>
+        <v>68265.53503471646</v>
       </c>
       <c r="R37" t="n">
         <v>21706658.10427722</v>
@@ -5101,22 +5101,22 @@
         <v>85057.43771268504</v>
       </c>
       <c r="T37" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V37" t="n">
-        <v>9016583.533606743</v>
+        <v>8710682.27042982</v>
       </c>
       <c r="W37" t="n">
-        <v>6511997.431283167</v>
+        <v>10853329.05213861</v>
       </c>
       <c r="X37" t="n">
-        <v>15528580.96488991</v>
+        <v>19564011.32256843</v>
       </c>
       <c r="Y37" t="n">
-        <v>60848.67149251532</v>
+        <v>76661.48637370075</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5134,13 +5134,13 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5150,13 +5150,13 @@
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ37" t="n">
-        <v>15528580.96488991</v>
+        <v>19172731.09611706</v>
       </c>
       <c r="AK37" t="n">
-        <v>60848.67149251532</v>
+        <v>75128.25664622674</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>13050598.20619388</v>
+        <v>17728762.2201193</v>
       </c>
       <c r="Q38" t="n">
-        <v>50175.31028909604</v>
+        <v>68161.33110388041</v>
       </c>
       <c r="R38" t="n">
         <v>22152250.92142075</v>
@@ -5229,22 +5229,22 @@
         <v>85168.20807928006</v>
       </c>
       <c r="T38" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V38" t="n">
-        <v>9135418.744335715</v>
+        <v>8864381.110059649</v>
       </c>
       <c r="W38" t="n">
-        <v>6645675.276426223</v>
+        <v>11076125.46071037</v>
       </c>
       <c r="X38" t="n">
-        <v>15781094.02076194</v>
+        <v>19940506.57077002</v>
       </c>
       <c r="Y38" t="n">
-        <v>60673.17962615124</v>
+        <v>76664.76959158023</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5262,13 +5262,13 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5278,13 +5278,13 @@
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ38" t="n">
-        <v>15781094.02076194</v>
+        <v>19541696.43935462</v>
       </c>
       <c r="AK38" t="n">
-        <v>60673.17962615124</v>
+        <v>75131.47419974863</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10102263.47281404</v>
+        <v>12104917.24206561</v>
       </c>
       <c r="Q39" t="n">
-        <v>59390.14387309841</v>
+        <v>71163.53463883368</v>
       </c>
       <c r="R39" t="n">
         <v>14046046.54011757</v>
@@ -5357,22 +5357,22 @@
         <v>82575.22951274294</v>
       </c>
       <c r="T39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V39" t="n">
-        <v>7071584.430969827</v>
+        <v>6052458.621032804</v>
       </c>
       <c r="W39" t="n">
-        <v>4213813.962035271</v>
+        <v>7023023.270058786</v>
       </c>
       <c r="X39" t="n">
-        <v>11285398.3930051</v>
+        <v>13075481.89109159</v>
       </c>
       <c r="Y39" t="n">
-        <v>66345.66956499177</v>
+        <v>76869.38207578831</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5406,13 +5406,13 @@
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ39" t="n">
-        <v>11285398.3930051</v>
+        <v>12813972.25326976</v>
       </c>
       <c r="AK39" t="n">
-        <v>66345.66956499177</v>
+        <v>75331.99443427254</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>9364255.722489627</v>
+        <v>11339004.01894366</v>
       </c>
       <c r="Q40" t="n">
-        <v>59043.22649741254</v>
+        <v>71494.35068690831</v>
       </c>
       <c r="R40" t="n">
         <v>13296305.5468278</v>
@@ -5481,22 +5481,22 @@
         <v>83835.47003044009</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V40" t="n">
-        <v>6554979.005742739</v>
+        <v>5669502.009471828</v>
       </c>
       <c r="W40" t="n">
-        <v>3988891.664048339</v>
+        <v>6648152.773413899</v>
       </c>
       <c r="X40" t="n">
-        <v>10543870.66979108</v>
+        <v>12317654.78288573</v>
       </c>
       <c r="Y40" t="n">
-        <v>66480.89955732079</v>
+        <v>77664.9103586742</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ40" t="n">
-        <v>10543870.66979108</v>
+        <v>12071301.68722801</v>
       </c>
       <c r="AK40" t="n">
-        <v>66480.89955732079</v>
+        <v>76111.6121515007</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>

--- a/data/processed/apartment_pricing_recommendations.xlsx
+++ b/data/processed/apartment_pricing_recommendations.xlsx
@@ -673,22 +673,22 @@
         <v>116351.1520137065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>2141759.780352378</v>
+        <v>2998463.692493329</v>
       </c>
       <c r="W2" t="n">
-        <v>4118830.781285209</v>
+        <v>2471298.468771125</v>
       </c>
       <c r="X2" t="n">
-        <v>6260590.561637588</v>
+        <v>5469762.161264455</v>
       </c>
       <c r="Y2" t="n">
-        <v>88426.42036211283</v>
+        <v>77256.52770147535</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6135378.750404836</v>
+        <v>5360366.918039165</v>
       </c>
       <c r="AK2" t="n">
-        <v>86657.89195487056</v>
+        <v>75711.39714744584</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -801,22 +801,22 @@
         <v>109347.8552969606</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1978650.80768399</v>
+        <v>2770111.130757586</v>
       </c>
       <c r="W3" t="n">
-        <v>3586609.653740306</v>
+        <v>2151965.792244183</v>
       </c>
       <c r="X3" t="n">
-        <v>5565260.461424297</v>
+        <v>4922076.92300177</v>
       </c>
       <c r="Y3" t="n">
-        <v>84836.28752171184</v>
+        <v>75031.66041161235</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -853,10 +853,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5453955.252195811</v>
+        <v>4823635.384541734</v>
       </c>
       <c r="AK3" t="n">
-        <v>83139.56177127761</v>
+        <v>73531.0272033801</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -929,22 +929,22 @@
         <v>88508.23686668056</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1697776.238037175</v>
+        <v>2376886.733252045</v>
       </c>
       <c r="W4" t="n">
-        <v>2522484.750700396</v>
+        <v>1513490.850420238</v>
       </c>
       <c r="X4" t="n">
-        <v>4220260.988737571</v>
+        <v>3890377.583672282</v>
       </c>
       <c r="Y4" t="n">
-        <v>74039.6664690802</v>
+        <v>68252.23831004003</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4135855.76896282</v>
+        <v>3812570.031998836</v>
       </c>
       <c r="AK4" t="n">
-        <v>72558.87313969858</v>
+        <v>66887.19354383924</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1053,22 +1053,22 @@
         <v>81115.30850722632</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2168796.217093366</v>
+        <v>3036314.703930712</v>
       </c>
       <c r="W5" t="n">
-        <v>2798478.143499308</v>
+        <v>1679086.886099585</v>
       </c>
       <c r="X5" t="n">
-        <v>4967274.360592674</v>
+        <v>4715401.590030297</v>
       </c>
       <c r="Y5" t="n">
-        <v>71989.48348685035</v>
+        <v>68339.15347869995</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4867928.873380821</v>
+        <v>4621093.55822969</v>
       </c>
       <c r="AK5" t="n">
-        <v>70549.69381711335</v>
+        <v>66972.37040912594</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1181,22 +1181,22 @@
         <v>81528.7335086055</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2168796.217093366</v>
+        <v>3036314.703930712</v>
       </c>
       <c r="W6" t="n">
-        <v>2812741.30604689</v>
+        <v>1687644.783628134</v>
       </c>
       <c r="X6" t="n">
-        <v>4981537.523140255</v>
+        <v>4723959.487558845</v>
       </c>
       <c r="Y6" t="n">
-        <v>72196.19598753993</v>
+        <v>68463.18097911371</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4881906.77267745</v>
+        <v>4629480.297807668</v>
       </c>
       <c r="AK6" t="n">
-        <v>70752.27206778913</v>
+        <v>67093.91735953142</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1309,22 +1309,22 @@
         <v>81114.04109832525</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>2168796.217093366</v>
+        <v>3036314.703930712</v>
       </c>
       <c r="W7" t="n">
-        <v>2798434.417892221</v>
+        <v>1679060.650735333</v>
       </c>
       <c r="X7" t="n">
-        <v>4967230.634985587</v>
+        <v>4715375.354666045</v>
       </c>
       <c r="Y7" t="n">
-        <v>71988.8497823998</v>
+        <v>68338.77325602964</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4867886.022285875</v>
+        <v>4621067.847572724</v>
       </c>
       <c r="AK7" t="n">
-        <v>70549.07278675181</v>
+        <v>66971.99779090905</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1437,22 +1437,22 @@
         <v>79214.26887609315</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V8" t="n">
-        <v>3511586.398587545</v>
+        <v>4916220.958022563</v>
       </c>
       <c r="W8" t="n">
-        <v>4400352.636066974</v>
+        <v>2640211.581640184</v>
       </c>
       <c r="X8" t="n">
-        <v>7911939.03465452</v>
+        <v>7556432.539662747</v>
       </c>
       <c r="Y8" t="n">
-        <v>71214.5727691676</v>
+        <v>68014.69432639737</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7753700.253961429</v>
+        <v>7405303.888869491</v>
       </c>
       <c r="AK8" t="n">
-        <v>69790.28131378425</v>
+        <v>66654.40043986941</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1565,22 +1565,22 @@
         <v>81579.71457299804</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V9" t="n">
-        <v>2252293.452065718</v>
+        <v>3153210.832892005</v>
       </c>
       <c r="W9" t="n">
-        <v>2814500.152768433</v>
+        <v>1688700.09166106</v>
       </c>
       <c r="X9" t="n">
-        <v>5066793.604834151</v>
+        <v>4841910.924553065</v>
       </c>
       <c r="Y9" t="n">
-        <v>73431.79137440799</v>
+        <v>70172.62209497196</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4965457.732737468</v>
+        <v>4745072.706062003</v>
       </c>
       <c r="AK9" t="n">
-        <v>71963.15554691982</v>
+        <v>68769.1696530725</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1689,22 +1689,22 @@
         <v>83400.09601120026</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V10" t="n">
-        <v>2252293.452065718</v>
+        <v>3153210.832892005</v>
       </c>
       <c r="W10" t="n">
-        <v>2877303.312386409</v>
+        <v>1726381.987431846</v>
       </c>
       <c r="X10" t="n">
-        <v>5129596.764452128</v>
+        <v>4879592.820323851</v>
       </c>
       <c r="Y10" t="n">
-        <v>74341.9820935091</v>
+        <v>70718.73652643262</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5027004.829163085</v>
+        <v>4782000.963917374</v>
       </c>
       <c r="AK10" t="n">
-        <v>72855.14245163891</v>
+        <v>69304.36179590397</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1817,22 +1817,22 @@
         <v>83053.49458977176</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V11" t="n">
-        <v>2252293.452065718</v>
+        <v>3153210.832892005</v>
       </c>
       <c r="W11" t="n">
-        <v>2865345.563347125</v>
+        <v>1719207.338008275</v>
       </c>
       <c r="X11" t="n">
-        <v>5117639.015412844</v>
+        <v>4872418.170900281</v>
       </c>
       <c r="Y11" t="n">
-        <v>74168.68138279484</v>
+        <v>70614.75610000407</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5015286.235104587</v>
+        <v>4774969.807482275</v>
       </c>
       <c r="AK11" t="n">
-        <v>72685.30775513894</v>
+        <v>69202.46097800399</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -1945,22 +1945,22 @@
         <v>79972.06971325737</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V12" t="n">
-        <v>3595083.633559898</v>
+        <v>5033117.086983857</v>
       </c>
       <c r="W12" t="n">
-        <v>4442448.472571447</v>
+        <v>2665469.083542868</v>
       </c>
       <c r="X12" t="n">
-        <v>8037532.106131345</v>
+        <v>7698586.170526724</v>
       </c>
       <c r="Y12" t="n">
-        <v>72345.02345752786</v>
+        <v>69294.20495523604</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7876781.464008718</v>
+        <v>7544614.44711619</v>
       </c>
       <c r="AK12" t="n">
-        <v>70898.1229883773</v>
+        <v>67908.32085613132</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -2069,22 +2069,22 @@
         <v>81633.38115903844</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>2335790.687038071</v>
+        <v>3270106.961853298</v>
       </c>
       <c r="W13" t="n">
-        <v>2816351.649986826</v>
+        <v>1689810.989992096</v>
       </c>
       <c r="X13" t="n">
-        <v>5152142.337024897</v>
+        <v>4959917.951845394</v>
       </c>
       <c r="Y13" t="n">
-        <v>74668.72952209997</v>
+        <v>71882.86886732456</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5049099.490284399</v>
+        <v>4860719.592808487</v>
       </c>
       <c r="AK13" t="n">
-        <v>73175.35493165796</v>
+        <v>70445.21148997807</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2193,22 +2193,22 @@
         <v>82046.80616041762</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V14" t="n">
-        <v>2335790.687038071</v>
+        <v>3270106.961853298</v>
       </c>
       <c r="W14" t="n">
-        <v>2830614.812534408</v>
+        <v>1698368.887520645</v>
       </c>
       <c r="X14" t="n">
-        <v>5166405.499572478</v>
+        <v>4968475.849373943</v>
       </c>
       <c r="Y14" t="n">
-        <v>74875.44202278955</v>
+        <v>72006.8963677383</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5063077.389581028</v>
+        <v>4869106.332386464</v>
       </c>
       <c r="AK14" t="n">
-        <v>73377.93318233374</v>
+        <v>70566.75844038354</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2317,22 +2317,22 @@
         <v>81632.11375013737</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V15" t="n">
-        <v>2335790.687038071</v>
+        <v>3270106.961853298</v>
       </c>
       <c r="W15" t="n">
-        <v>2816307.924379739</v>
+        <v>1689784.754627844</v>
       </c>
       <c r="X15" t="n">
-        <v>5152098.61141781</v>
+        <v>4959891.716481142</v>
       </c>
       <c r="Y15" t="n">
-        <v>74668.09581764942</v>
+        <v>71882.48864465422</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5049056.639189453</v>
+        <v>4860693.882151519</v>
       </c>
       <c r="AK15" t="n">
-        <v>73174.73390129642</v>
+        <v>70444.83887176114</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -2445,22 +2445,22 @@
         <v>79536.02416839769</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V16" t="n">
-        <v>3678580.86853225</v>
+        <v>5150013.21594515</v>
       </c>
       <c r="W16" t="n">
-        <v>4418226.142554492</v>
+        <v>2650935.685532695</v>
       </c>
       <c r="X16" t="n">
-        <v>8096807.011086741</v>
+        <v>7800948.901477845</v>
       </c>
       <c r="Y16" t="n">
-        <v>72878.55095487616</v>
+        <v>70215.56166946756</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7934870.870865007</v>
+        <v>7644929.923448288</v>
       </c>
       <c r="AK16" t="n">
-        <v>71420.97993577864</v>
+        <v>68811.2504360782</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -2569,22 +2569,22 @@
         <v>82097.78722481016</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>2419287.922010423</v>
+        <v>3387003.090814592</v>
       </c>
       <c r="W17" t="n">
-        <v>2832373.659255951</v>
+        <v>1699424.19555357</v>
       </c>
       <c r="X17" t="n">
-        <v>5251661.581266373</v>
+        <v>5086427.286368162</v>
       </c>
       <c r="Y17" t="n">
-        <v>76111.03740965758</v>
+        <v>73716.33748359655</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5146628.349641046</v>
+        <v>4984698.740640799</v>
       </c>
       <c r="AK17" t="n">
-        <v>74588.81666146443</v>
+        <v>72242.01073392462</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -2697,22 +2697,22 @@
         <v>83918.16866301239</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V18" t="n">
-        <v>2419287.922010423</v>
+        <v>3387003.090814592</v>
       </c>
       <c r="W18" t="n">
-        <v>2895176.818873927</v>
+        <v>1737106.091324356</v>
       </c>
       <c r="X18" t="n">
-        <v>5314464.740884351</v>
+        <v>5124109.182138949</v>
       </c>
       <c r="Y18" t="n">
-        <v>77021.22812875871</v>
+        <v>74262.45191505723</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5208175.446066664</v>
+        <v>5021626.998496169</v>
       </c>
       <c r="AK18" t="n">
-        <v>75480.80356618353</v>
+        <v>72777.20287675607</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -2825,22 +2825,22 @@
         <v>83571.56724158386</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V19" t="n">
-        <v>2419287.922010423</v>
+        <v>3387003.090814592</v>
       </c>
       <c r="W19" t="n">
-        <v>2883219.069834644</v>
+        <v>1729931.441900786</v>
       </c>
       <c r="X19" t="n">
-        <v>5302506.991845067</v>
+        <v>5116934.532715378</v>
       </c>
       <c r="Y19" t="n">
-        <v>76847.92741804445</v>
+        <v>74158.47148862867</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ19" t="n">
-        <v>5196456.852008165</v>
+        <v>5014595.842061071</v>
       </c>
       <c r="AK19" t="n">
-        <v>75310.96886968355</v>
+        <v>72675.30205885609</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -2953,22 +2953,22 @@
         <v>80293.82500556191</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V20" t="n">
-        <v>3762078.103504602</v>
+        <v>5266909.344906443</v>
       </c>
       <c r="W20" t="n">
-        <v>4460321.979058964</v>
+        <v>2676193.187435378</v>
       </c>
       <c r="X20" t="n">
-        <v>8222400.082563566</v>
+        <v>7943102.532341821</v>
       </c>
       <c r="Y20" t="n">
-        <v>74009.00164323642</v>
+        <v>71495.07229830623</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8057952.080912295</v>
+        <v>7784240.481694984</v>
       </c>
       <c r="AK20" t="n">
-        <v>72528.8216103717</v>
+        <v>70065.1708523401</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -3081,22 +3081,22 @@
         <v>82151.45381085057</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V21" t="n">
-        <v>2502785.156982775</v>
+        <v>3503899.219775885</v>
       </c>
       <c r="W21" t="n">
-        <v>2834225.156474344</v>
+        <v>1700535.093884607</v>
       </c>
       <c r="X21" t="n">
-        <v>5337010.31345712</v>
+        <v>5204434.313660492</v>
       </c>
       <c r="Y21" t="n">
-        <v>77347.97555734956</v>
+        <v>75426.58425594916</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5230270.107187978</v>
+        <v>5100345.627387282</v>
       </c>
       <c r="AK21" t="n">
-        <v>75801.01604620258</v>
+        <v>73918.05257083019</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -3205,22 +3205,22 @@
         <v>82564.87881222973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V22" t="n">
-        <v>2502785.156982775</v>
+        <v>3503899.219775885</v>
       </c>
       <c r="W22" t="n">
-        <v>2848488.319021926</v>
+        <v>1709092.991413155</v>
       </c>
       <c r="X22" t="n">
-        <v>5351273.476004701</v>
+        <v>5212992.211189041</v>
       </c>
       <c r="Y22" t="n">
-        <v>77554.68805803914</v>
+        <v>75550.61175636291</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5244248.006484607</v>
+        <v>5108732.36696526</v>
       </c>
       <c r="AK22" t="n">
-        <v>76003.59429687836</v>
+        <v>74039.59952123565</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -3333,22 +3333,22 @@
         <v>82150.1864019495</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V23" t="n">
-        <v>2502785.156982775</v>
+        <v>3503899.219775885</v>
       </c>
       <c r="W23" t="n">
-        <v>2834181.430867258</v>
+        <v>1700508.858520354</v>
       </c>
       <c r="X23" t="n">
-        <v>5336966.587850032</v>
+        <v>5204408.078296239</v>
       </c>
       <c r="Y23" t="n">
-        <v>77347.34185289902</v>
+        <v>75426.20403327883</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5230227.256093032</v>
+        <v>5100319.916730314</v>
       </c>
       <c r="AK23" t="n">
-        <v>75800.39501584104</v>
+        <v>73917.67995261325</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -3461,22 +3461,22 @@
         <v>79857.77946070227</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V24" t="n">
-        <v>3845575.338476955</v>
+        <v>5383805.473867737</v>
       </c>
       <c r="W24" t="n">
-        <v>4436099.64904201</v>
+        <v>2661659.789425206</v>
       </c>
       <c r="X24" t="n">
-        <v>8281674.987518965</v>
+        <v>8045465.263292942</v>
       </c>
       <c r="Y24" t="n">
-        <v>74542.52914058475</v>
+        <v>72416.42901253773</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8116041.487768586</v>
+        <v>7884555.958027083</v>
       </c>
       <c r="AK24" t="n">
-        <v>73051.67855777305</v>
+        <v>70968.10043228698</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -3589,22 +3589,22 @@
         <v>82615.85987662229</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V25" t="n">
-        <v>2586282.391955127</v>
+        <v>3620795.348737178</v>
       </c>
       <c r="W25" t="n">
-        <v>2850247.165743469</v>
+        <v>1710148.299446081</v>
       </c>
       <c r="X25" t="n">
-        <v>5436529.557698596</v>
+        <v>5330943.64818326</v>
       </c>
       <c r="Y25" t="n">
-        <v>78790.2834449072</v>
+        <v>77260.05287222116</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5327798.966544624</v>
+        <v>5224324.775219595</v>
       </c>
       <c r="AK25" t="n">
-        <v>77214.47777600905</v>
+        <v>75714.85181477675</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -3713,22 +3713,22 @@
         <v>84436.24131482451</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V26" t="n">
-        <v>2586282.391955127</v>
+        <v>3620795.348737178</v>
       </c>
       <c r="W26" t="n">
-        <v>2913050.325361446</v>
+        <v>1747830.195216867</v>
       </c>
       <c r="X26" t="n">
-        <v>5499332.717316573</v>
+        <v>5368625.543954046</v>
       </c>
       <c r="Y26" t="n">
-        <v>79700.47416400831</v>
+        <v>77806.16730368182</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ26" t="n">
-        <v>5389346.062970242</v>
+        <v>5261253.033074965</v>
       </c>
       <c r="AK26" t="n">
-        <v>78106.46468072814</v>
+        <v>76250.04395760818</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -3841,22 +3841,22 @@
         <v>84089.63989339599</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V27" t="n">
-        <v>2586282.391955127</v>
+        <v>3620795.348737178</v>
       </c>
       <c r="W27" t="n">
-        <v>2901092.576322162</v>
+        <v>1740655.545793297</v>
       </c>
       <c r="X27" t="n">
-        <v>5487374.968277289</v>
+        <v>5361450.894530475</v>
       </c>
       <c r="Y27" t="n">
-        <v>79527.17345329403</v>
+        <v>77702.18687725326</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5377627.468911743</v>
+        <v>5254221.876639865</v>
       </c>
       <c r="AK27" t="n">
-        <v>77936.62998422816</v>
+        <v>76148.14313970819</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -3969,22 +3969,22 @@
         <v>80615.58029786649</v>
       </c>
       <c r="T28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V28" t="n">
-        <v>3929072.573449307</v>
+        <v>5500701.60282903</v>
       </c>
       <c r="W28" t="n">
-        <v>4478195.485546483</v>
+        <v>2686917.29132789</v>
       </c>
       <c r="X28" t="n">
-        <v>8407268.058995791</v>
+        <v>8187618.89415692</v>
       </c>
       <c r="Y28" t="n">
-        <v>75672.97982894501</v>
+        <v>73695.93964137642</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8239122.697815875</v>
+        <v>8023866.516273782</v>
       </c>
       <c r="AK28" t="n">
-        <v>74159.52023236611</v>
+        <v>72222.0208485489</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -4093,22 +4093,22 @@
         <v>82669.52646266269</v>
       </c>
       <c r="T29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V29" t="n">
-        <v>2669779.62692748</v>
+        <v>3737691.477698471</v>
       </c>
       <c r="W29" t="n">
-        <v>2852098.662961863</v>
+        <v>1711259.197777117</v>
       </c>
       <c r="X29" t="n">
-        <v>5521878.289889342</v>
+        <v>5448950.675475589</v>
       </c>
       <c r="Y29" t="n">
-        <v>80027.22159259916</v>
+        <v>78970.29964457375</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ29" t="n">
-        <v>5411440.724091555</v>
+        <v>5339971.661966077</v>
       </c>
       <c r="AK29" t="n">
-        <v>78426.67716074717</v>
+        <v>77390.89365168227</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -4217,22 +4217,22 @@
         <v>83082.95146404185</v>
       </c>
       <c r="T30" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V30" t="n">
-        <v>2669779.62692748</v>
+        <v>3737691.477698471</v>
       </c>
       <c r="W30" t="n">
-        <v>2866361.825509444</v>
+        <v>1719817.095305666</v>
       </c>
       <c r="X30" t="n">
-        <v>5536141.452436924</v>
+        <v>5457508.573004138</v>
       </c>
       <c r="Y30" t="n">
-        <v>80233.93409328876</v>
+        <v>79094.3271449875</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ30" t="n">
-        <v>5425418.623388185</v>
+        <v>5348358.401544055</v>
       </c>
       <c r="AK30" t="n">
-        <v>78629.25541142297</v>
+        <v>77512.44060208775</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -4345,22 +4345,22 @@
         <v>82668.25905376161</v>
       </c>
       <c r="T31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U31" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V31" t="n">
-        <v>2669779.62692748</v>
+        <v>3737691.477698471</v>
       </c>
       <c r="W31" t="n">
-        <v>2852054.937354776</v>
+        <v>1711232.962412865</v>
       </c>
       <c r="X31" t="n">
-        <v>5521834.564282255</v>
+        <v>5448924.440111337</v>
       </c>
       <c r="Y31" t="n">
-        <v>80026.58788814863</v>
+        <v>78969.91942190344</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -4397,10 +4397,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5411397.87299661</v>
+        <v>5339945.95130911</v>
       </c>
       <c r="AK31" t="n">
-        <v>78426.05613038565</v>
+        <v>77390.52103346537</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -4473,22 +4473,22 @@
         <v>80179.53475300681</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U32" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V32" t="n">
-        <v>4012569.808421659</v>
+        <v>5617597.731790323</v>
       </c>
       <c r="W32" t="n">
-        <v>4453973.155529528</v>
+        <v>2672383.893317717</v>
       </c>
       <c r="X32" t="n">
-        <v>8466542.963951187</v>
+        <v>8289981.625108039</v>
       </c>
       <c r="Y32" t="n">
-        <v>76206.50732629331</v>
+        <v>74617.29635560792</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ32" t="n">
-        <v>8297212.104672164</v>
+        <v>8124181.992605878</v>
       </c>
       <c r="AK32" t="n">
-        <v>74682.37717976746</v>
+        <v>73124.95042849575</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -4597,22 +4597,22 @@
         <v>83133.93252843441</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U33" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V33" t="n">
-        <v>2753276.861899832</v>
+        <v>3854587.606659765</v>
       </c>
       <c r="W33" t="n">
-        <v>2868120.672230987</v>
+        <v>1720872.403338592</v>
       </c>
       <c r="X33" t="n">
-        <v>5621397.534130819</v>
+        <v>5575460.009998357</v>
       </c>
       <c r="Y33" t="n">
-        <v>81469.52948015679</v>
+        <v>80803.76826084575</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -4649,10 +4649,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ33" t="n">
-        <v>5508969.583448202</v>
+        <v>5463950.80979839</v>
       </c>
       <c r="AK33" t="n">
-        <v>79840.13889055366</v>
+        <v>79187.69289562883</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -4721,22 +4721,22 @@
         <v>84954.31396663663</v>
       </c>
       <c r="T34" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V34" t="n">
-        <v>2753276.861899832</v>
+        <v>3854587.606659765</v>
       </c>
       <c r="W34" t="n">
-        <v>2930923.831848964</v>
+        <v>1758554.299109378</v>
       </c>
       <c r="X34" t="n">
-        <v>5684200.693748796</v>
+        <v>5613141.905769143</v>
       </c>
       <c r="Y34" t="n">
-        <v>82379.72019925792</v>
+        <v>81349.88269230642</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ34" t="n">
-        <v>5570516.67987382</v>
+        <v>5500879.06765376</v>
       </c>
       <c r="AK34" t="n">
-        <v>80732.12579527276</v>
+        <v>79722.8850384603</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
@@ -4845,22 +4845,22 @@
         <v>84607.71254520811</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U35" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V35" t="n">
-        <v>2753276.861899832</v>
+        <v>3854587.606659765</v>
       </c>
       <c r="W35" t="n">
-        <v>2918966.08280968</v>
+        <v>1751379.649685808</v>
       </c>
       <c r="X35" t="n">
-        <v>5672242.944709511</v>
+        <v>5605967.256345573</v>
       </c>
       <c r="Y35" t="n">
-        <v>82206.41948854364</v>
+        <v>81245.90226587787</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5558798.085815321</v>
+        <v>5493847.911218661</v>
       </c>
       <c r="AK35" t="n">
-        <v>80562.29109877277</v>
+        <v>79620.98422056031</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -4973,22 +4973,22 @@
         <v>80937.33559017103</v>
       </c>
       <c r="T36" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V36" t="n">
-        <v>4096067.043394012</v>
+        <v>5734493.860751617</v>
       </c>
       <c r="W36" t="n">
-        <v>4496068.992034</v>
+        <v>2697641.3952204</v>
       </c>
       <c r="X36" t="n">
-        <v>8592136.035428012</v>
+        <v>8432135.255972017</v>
       </c>
       <c r="Y36" t="n">
-        <v>77336.95801465357</v>
+        <v>75896.80698444659</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -5025,10 +5025,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ36" t="n">
-        <v>8420293.314719452</v>
+        <v>8263492.550852576</v>
       </c>
       <c r="AK36" t="n">
-        <v>75790.2188543605</v>
+        <v>74378.87084475766</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -5101,22 +5101,22 @@
         <v>85057.43771268504</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U37" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V37" t="n">
-        <v>8710682.27042982</v>
+        <v>12194955.17860175</v>
       </c>
       <c r="W37" t="n">
-        <v>10853329.05213861</v>
+        <v>6511997.431283167</v>
       </c>
       <c r="X37" t="n">
-        <v>19564011.32256843</v>
+        <v>18706952.60988491</v>
       </c>
       <c r="Y37" t="n">
-        <v>76661.48637370075</v>
+        <v>73303.10583810703</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ37" t="n">
-        <v>19172731.09611706</v>
+        <v>18332813.55768722</v>
       </c>
       <c r="AK37" t="n">
-        <v>75128.25664622674</v>
+        <v>71837.04372134489</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -5229,22 +5229,22 @@
         <v>85168.20807928006</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V38" t="n">
-        <v>8864381.110059649</v>
+        <v>12410133.55408351</v>
       </c>
       <c r="W38" t="n">
-        <v>11076125.46071037</v>
+        <v>6645675.276426223</v>
       </c>
       <c r="X38" t="n">
-        <v>19940506.57077002</v>
+        <v>19055808.83050973</v>
       </c>
       <c r="Y38" t="n">
-        <v>76664.76959158023</v>
+        <v>73263.3941965003</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ38" t="n">
-        <v>19541696.43935462</v>
+        <v>18674692.65389954</v>
       </c>
       <c r="AK38" t="n">
-        <v>75131.47419974863</v>
+        <v>71798.1263125703</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -5357,22 +5357,22 @@
         <v>82575.22951274294</v>
       </c>
       <c r="T39" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V39" t="n">
-        <v>6052458.621032804</v>
+        <v>8473442.069445925</v>
       </c>
       <c r="W39" t="n">
-        <v>7023023.270058786</v>
+        <v>4213813.962035271</v>
       </c>
       <c r="X39" t="n">
-        <v>13075481.89109159</v>
+        <v>12687256.0314812</v>
       </c>
       <c r="Y39" t="n">
-        <v>76869.38207578831</v>
+        <v>74587.04310100643</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ39" t="n">
-        <v>12813972.25326976</v>
+        <v>12433510.91085157</v>
       </c>
       <c r="AK39" t="n">
-        <v>75331.99443427254</v>
+        <v>73095.30223898632</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -5481,22 +5481,22 @@
         <v>83835.47003044009</v>
       </c>
       <c r="T40" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="U40" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="V40" t="n">
-        <v>5669502.009471828</v>
+        <v>7937302.813260559</v>
       </c>
       <c r="W40" t="n">
-        <v>6648152.773413899</v>
+        <v>3988891.664048339</v>
       </c>
       <c r="X40" t="n">
-        <v>12317654.78288573</v>
+        <v>11926194.4773089</v>
       </c>
       <c r="Y40" t="n">
-        <v>77664.9103586742</v>
+        <v>75196.68648996785</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ40" t="n">
-        <v>12071301.68722801</v>
+        <v>11687670.58776272</v>
       </c>
       <c r="AK40" t="n">
-        <v>76111.6121515007</v>
+        <v>73692.75276016849</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>

--- a/data/processed/apartment_pricing_recommendations.xlsx
+++ b/data/processed/apartment_pricing_recommendations.xlsx
@@ -667,10 +667,10 @@
         <v>60501.68871051916</v>
       </c>
       <c r="R2" t="n">
-        <v>8237661.562570418</v>
+        <v>8991312.544811539</v>
       </c>
       <c r="S2" t="n">
-        <v>116351.1520137065</v>
+        <v>126995.9398984681</v>
       </c>
       <c r="T2" t="n">
         <v>0.7</v>
@@ -682,13 +682,13 @@
         <v>2998463.692493329</v>
       </c>
       <c r="W2" t="n">
-        <v>2471298.468771125</v>
+        <v>2697393.763443462</v>
       </c>
       <c r="X2" t="n">
-        <v>5469762.161264455</v>
+        <v>5695857.455936791</v>
       </c>
       <c r="Y2" t="n">
-        <v>77256.52770147535</v>
+        <v>80449.96406690383</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5360366.918039165</v>
+        <v>5581940.306818055</v>
       </c>
       <c r="AK2" t="n">
-        <v>75711.39714744584</v>
+        <v>78840.96478556575</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         <v>60324.71974646312</v>
       </c>
       <c r="R3" t="n">
-        <v>7173219.307480612</v>
+        <v>8138616.855513262</v>
       </c>
       <c r="S3" t="n">
-        <v>109347.8552969606</v>
+        <v>124064.2813340436</v>
       </c>
       <c r="T3" t="n">
         <v>0.7</v>
@@ -810,13 +810,13 @@
         <v>2770111.130757586</v>
       </c>
       <c r="W3" t="n">
-        <v>2151965.792244183</v>
+        <v>2441585.056653978</v>
       </c>
       <c r="X3" t="n">
-        <v>4922076.92300177</v>
+        <v>5211696.187411564</v>
       </c>
       <c r="Y3" t="n">
-        <v>75031.66041161235</v>
+        <v>79446.58822273726</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -853,10 +853,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4823635.384541734</v>
+        <v>5107462.263663333</v>
       </c>
       <c r="AK3" t="n">
-        <v>73531.0272033801</v>
+        <v>77857.65645828252</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>59571.09607147983</v>
       </c>
       <c r="R4" t="n">
-        <v>5044969.501400792</v>
+        <v>6606605.455239789</v>
       </c>
       <c r="S4" t="n">
-        <v>88508.23686668056</v>
+        <v>115905.3588638559</v>
       </c>
       <c r="T4" t="n">
         <v>0.7</v>
@@ -938,13 +938,13 @@
         <v>2376886.733252045</v>
       </c>
       <c r="W4" t="n">
-        <v>1513490.850420238</v>
+        <v>1981981.636571937</v>
       </c>
       <c r="X4" t="n">
-        <v>3890377.583672282</v>
+        <v>4358868.369823981</v>
       </c>
       <c r="Y4" t="n">
-        <v>68252.23831004003</v>
+        <v>76471.37490919264</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3812570.031998836</v>
+        <v>4271691.002427502</v>
       </c>
       <c r="AK4" t="n">
-        <v>66887.19354383924</v>
+        <v>74941.9474110088</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         <v>62863.65846647437</v>
       </c>
       <c r="R5" t="n">
-        <v>5596956.286998617</v>
+        <v>6144127.982743562</v>
       </c>
       <c r="S5" t="n">
-        <v>81115.30850722632</v>
+        <v>89045.33308324004</v>
       </c>
       <c r="T5" t="n">
         <v>0.7</v>
@@ -1062,13 +1062,13 @@
         <v>3036314.703930712</v>
       </c>
       <c r="W5" t="n">
-        <v>1679086.886099585</v>
+        <v>1843238.394823069</v>
       </c>
       <c r="X5" t="n">
-        <v>4715401.590030297</v>
+        <v>4879553.09875378</v>
       </c>
       <c r="Y5" t="n">
-        <v>68339.15347869995</v>
+        <v>70718.16085150406</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4621093.55822969</v>
+        <v>4781962.036778704</v>
       </c>
       <c r="AK5" t="n">
-        <v>66972.37040912594</v>
+        <v>69303.79763447397</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         <v>62863.65846647437</v>
       </c>
       <c r="R6" t="n">
-        <v>5625482.612093779</v>
+        <v>6054762.214271542</v>
       </c>
       <c r="S6" t="n">
-        <v>81528.7335086055</v>
+        <v>87750.17701842813</v>
       </c>
       <c r="T6" t="n">
         <v>0.7</v>
@@ -1190,13 +1190,13 @@
         <v>3036314.703930712</v>
       </c>
       <c r="W6" t="n">
-        <v>1687644.783628134</v>
+        <v>1816428.664281463</v>
       </c>
       <c r="X6" t="n">
-        <v>4723959.487558845</v>
+        <v>4852743.368212175</v>
       </c>
       <c r="Y6" t="n">
-        <v>68463.18097911371</v>
+        <v>70329.6140320605</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4629480.297807668</v>
+        <v>4755688.500847931</v>
       </c>
       <c r="AK6" t="n">
-        <v>67093.91735953142</v>
+        <v>68923.02175141929</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1303,10 +1303,10 @@
         <v>62863.65846647437</v>
       </c>
       <c r="R7" t="n">
-        <v>5596868.835784443</v>
+        <v>5935631.324601264</v>
       </c>
       <c r="S7" t="n">
-        <v>81114.04109832525</v>
+        <v>86023.64238552556</v>
       </c>
       <c r="T7" t="n">
         <v>0.7</v>
@@ -1318,13 +1318,13 @@
         <v>3036314.703930712</v>
       </c>
       <c r="W7" t="n">
-        <v>1679060.650735333</v>
+        <v>1780689.397380379</v>
       </c>
       <c r="X7" t="n">
-        <v>4715375.354666045</v>
+        <v>4817004.101311091</v>
       </c>
       <c r="Y7" t="n">
-        <v>68338.77325602964</v>
+        <v>69811.65364218973</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4621067.847572724</v>
+        <v>4720664.01928487</v>
       </c>
       <c r="AK7" t="n">
-        <v>66971.99779090905</v>
+        <v>68415.42056934594</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>63214.87666224204</v>
       </c>
       <c r="R8" t="n">
-        <v>8800705.272133948</v>
+        <v>9476736.022945456</v>
       </c>
       <c r="S8" t="n">
-        <v>79214.26887609315</v>
+        <v>85299.1541219213</v>
       </c>
       <c r="T8" t="n">
         <v>0.7</v>
@@ -1446,13 +1446,13 @@
         <v>4916220.958022563</v>
       </c>
       <c r="W8" t="n">
-        <v>2640211.581640184</v>
+        <v>2843020.806883637</v>
       </c>
       <c r="X8" t="n">
-        <v>7556432.539662747</v>
+        <v>7759241.7649062</v>
       </c>
       <c r="Y8" t="n">
-        <v>68014.69432639737</v>
+        <v>69840.15990014581</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7405303.888869491</v>
+        <v>7604056.929608076</v>
       </c>
       <c r="AK8" t="n">
-        <v>66654.40043986941</v>
+        <v>68443.3567021429</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>65283.86817581792</v>
       </c>
       <c r="R9" t="n">
-        <v>5629000.305536865</v>
+        <v>6005397.143538642</v>
       </c>
       <c r="S9" t="n">
-        <v>81579.71457299804</v>
+        <v>87034.74121070495</v>
       </c>
       <c r="T9" t="n">
         <v>0.7</v>
@@ -1574,13 +1574,13 @@
         <v>3153210.832892005</v>
       </c>
       <c r="W9" t="n">
-        <v>1688700.09166106</v>
+        <v>1801619.143061592</v>
       </c>
       <c r="X9" t="n">
-        <v>4841910.924553065</v>
+        <v>4954829.975953598</v>
       </c>
       <c r="Y9" t="n">
-        <v>70172.62209497196</v>
+        <v>71809.13008628403</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4745072.706062003</v>
+        <v>4855733.376434525</v>
       </c>
       <c r="AK9" t="n">
-        <v>68769.1696530725</v>
+        <v>70372.94748455835</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>65283.86817581792</v>
       </c>
       <c r="R10" t="n">
-        <v>5754606.624772819</v>
+        <v>6307619.070107225</v>
       </c>
       <c r="S10" t="n">
-        <v>83400.09601120026</v>
+        <v>91414.76913198877</v>
       </c>
       <c r="T10" t="n">
         <v>0.7</v>
@@ -1698,13 +1698,13 @@
         <v>3153210.832892005</v>
       </c>
       <c r="W10" t="n">
-        <v>1726381.987431846</v>
+        <v>1892285.721032168</v>
       </c>
       <c r="X10" t="n">
-        <v>4879592.820323851</v>
+        <v>5045496.553924173</v>
       </c>
       <c r="Y10" t="n">
-        <v>70718.73652643262</v>
+        <v>73123.13846266917</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4782000.963917374</v>
+        <v>4944586.62284569</v>
       </c>
       <c r="AK10" t="n">
-        <v>69304.36179590397</v>
+        <v>71660.67569341579</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         <v>65283.86817581792</v>
       </c>
       <c r="R11" t="n">
-        <v>5730691.126694251</v>
+        <v>6296011.966243587</v>
       </c>
       <c r="S11" t="n">
-        <v>83053.49458977176</v>
+        <v>91246.5502354143</v>
       </c>
       <c r="T11" t="n">
         <v>0.7</v>
@@ -1826,13 +1826,13 @@
         <v>3153210.832892005</v>
       </c>
       <c r="W11" t="n">
-        <v>1719207.338008275</v>
+        <v>1888803.589873076</v>
       </c>
       <c r="X11" t="n">
-        <v>4872418.170900281</v>
+        <v>5042014.422765082</v>
       </c>
       <c r="Y11" t="n">
-        <v>70614.75610000407</v>
+        <v>73072.67279369684</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4774969.807482275</v>
+        <v>4941174.13430978</v>
       </c>
       <c r="AK11" t="n">
-        <v>69202.46097800399</v>
+        <v>71611.2193378229</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>64717.97720179835</v>
       </c>
       <c r="R12" t="n">
-        <v>8884896.945142893</v>
+        <v>9969762.287389144</v>
       </c>
       <c r="S12" t="n">
-        <v>79972.06971325737</v>
+        <v>89736.8342699293</v>
       </c>
       <c r="T12" t="n">
         <v>0.7</v>
@@ -1954,13 +1954,13 @@
         <v>5033117.086983857</v>
       </c>
       <c r="W12" t="n">
-        <v>2665469.083542868</v>
+        <v>2990928.686216743</v>
       </c>
       <c r="X12" t="n">
-        <v>7698586.170526724</v>
+        <v>8024045.773200599</v>
       </c>
       <c r="Y12" t="n">
-        <v>69294.20495523604</v>
+        <v>72223.63432223762</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7544614.44711619</v>
+        <v>7863564.857736588</v>
       </c>
       <c r="AK12" t="n">
-        <v>67908.32085613132</v>
+        <v>70779.16163579287</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         <v>67704.07788516146</v>
       </c>
       <c r="R13" t="n">
-        <v>5632703.299973653</v>
+        <v>6200228.826801076</v>
       </c>
       <c r="S13" t="n">
-        <v>81633.38115903844</v>
+        <v>89858.38879421848</v>
       </c>
       <c r="T13" t="n">
         <v>0.7</v>
@@ -2078,13 +2078,13 @@
         <v>3270106.961853298</v>
       </c>
       <c r="W13" t="n">
-        <v>1689810.989992096</v>
+        <v>1860068.648040323</v>
       </c>
       <c r="X13" t="n">
-        <v>4959917.951845394</v>
+        <v>5130175.609893621</v>
       </c>
       <c r="Y13" t="n">
-        <v>71882.86886732456</v>
+        <v>74350.37115787856</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4860719.592808487</v>
+        <v>5027572.097695748</v>
       </c>
       <c r="AK13" t="n">
-        <v>70445.21148997807</v>
+        <v>72863.36373472099</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>67704.07788516146</v>
       </c>
       <c r="R14" t="n">
-        <v>5661229.625068815</v>
+        <v>6110863.058329055</v>
       </c>
       <c r="S14" t="n">
-        <v>82046.80616041762</v>
+        <v>88563.23272940659</v>
       </c>
       <c r="T14" t="n">
         <v>0.7</v>
@@ -2202,13 +2202,13 @@
         <v>3270106.961853298</v>
       </c>
       <c r="W14" t="n">
-        <v>1698368.887520645</v>
+        <v>1833258.917498716</v>
       </c>
       <c r="X14" t="n">
-        <v>4968475.849373943</v>
+        <v>5103365.879352015</v>
       </c>
       <c r="Y14" t="n">
-        <v>72006.8963677383</v>
+        <v>73961.82433843499</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4869106.332386464</v>
+        <v>5001298.561764974</v>
       </c>
       <c r="AK14" t="n">
-        <v>70566.75844038354</v>
+        <v>72482.58785166629</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>67704.07788516146</v>
       </c>
       <c r="R15" t="n">
-        <v>5632615.848759479</v>
+        <v>5991732.168658777</v>
       </c>
       <c r="S15" t="n">
-        <v>81632.11375013737</v>
+        <v>86836.69809650401</v>
       </c>
       <c r="T15" t="n">
         <v>0.7</v>
@@ -2326,13 +2326,13 @@
         <v>3270106.961853298</v>
       </c>
       <c r="W15" t="n">
-        <v>1689784.754627844</v>
+        <v>1797519.650597633</v>
       </c>
       <c r="X15" t="n">
-        <v>4959891.716481142</v>
+        <v>5067626.612450931</v>
       </c>
       <c r="Y15" t="n">
-        <v>71882.48864465422</v>
+        <v>73443.86394856422</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4860693.882151519</v>
+        <v>4966274.080201913</v>
       </c>
       <c r="AK15" t="n">
-        <v>70444.83887176114</v>
+        <v>71974.98666959294</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         <v>66221.07774135465</v>
       </c>
       <c r="R16" t="n">
-        <v>8836452.285108984</v>
+        <v>9532836.867002968</v>
       </c>
       <c r="S16" t="n">
-        <v>79536.02416839769</v>
+        <v>85804.11221424813</v>
       </c>
       <c r="T16" t="n">
         <v>0.7</v>
@@ -2454,13 +2454,13 @@
         <v>5150013.21594515</v>
       </c>
       <c r="W16" t="n">
-        <v>2650935.685532695</v>
+        <v>2859851.06010089</v>
       </c>
       <c r="X16" t="n">
-        <v>7800948.901477845</v>
+        <v>8009864.27604604</v>
       </c>
       <c r="Y16" t="n">
-        <v>70215.56166946756</v>
+        <v>72095.98808322268</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7644929.923448288</v>
+        <v>7849666.990525119</v>
       </c>
       <c r="AK16" t="n">
-        <v>68811.2504360782</v>
+        <v>70654.06832155822</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         <v>70124.28759450502</v>
       </c>
       <c r="R17" t="n">
-        <v>5664747.318511901</v>
+        <v>6061497.987596154</v>
       </c>
       <c r="S17" t="n">
-        <v>82097.78722481016</v>
+        <v>87847.79692168339</v>
       </c>
       <c r="T17" t="n">
         <v>0.7</v>
@@ -2578,13 +2578,13 @@
         <v>3387003.090814592</v>
       </c>
       <c r="W17" t="n">
-        <v>1699424.19555357</v>
+        <v>1818449.396278846</v>
       </c>
       <c r="X17" t="n">
-        <v>5086427.286368162</v>
+        <v>5205452.487093438</v>
       </c>
       <c r="Y17" t="n">
-        <v>73716.33748359655</v>
+        <v>75441.34039265853</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4984698.740640799</v>
+        <v>5101343.43735157</v>
       </c>
       <c r="AK17" t="n">
-        <v>72242.01073392462</v>
+        <v>73932.51358480536</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         <v>70124.28759450502</v>
       </c>
       <c r="R18" t="n">
-        <v>5790353.637747855</v>
+        <v>6363719.914164739</v>
       </c>
       <c r="S18" t="n">
-        <v>83918.16866301239</v>
+        <v>92227.82484296722</v>
       </c>
       <c r="T18" t="n">
         <v>0.7</v>
@@ -2706,13 +2706,13 @@
         <v>3387003.090814592</v>
       </c>
       <c r="W18" t="n">
-        <v>1737106.091324356</v>
+        <v>1909115.974249422</v>
       </c>
       <c r="X18" t="n">
-        <v>5124109.182138949</v>
+        <v>5296119.065064014</v>
       </c>
       <c r="Y18" t="n">
-        <v>74262.45191505723</v>
+        <v>76755.34876904367</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5021626.998496169</v>
+        <v>5190196.683762734</v>
       </c>
       <c r="AK18" t="n">
-        <v>72777.20287675607</v>
+        <v>75220.2417936628</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
         <v>70124.28759450502</v>
       </c>
       <c r="R19" t="n">
-        <v>5766438.139669287</v>
+        <v>6352112.810301099</v>
       </c>
       <c r="S19" t="n">
-        <v>83571.56724158386</v>
+        <v>92059.60594639274</v>
       </c>
       <c r="T19" t="n">
         <v>0.7</v>
@@ -2834,13 +2834,13 @@
         <v>3387003.090814592</v>
       </c>
       <c r="W19" t="n">
-        <v>1729931.441900786</v>
+        <v>1905633.84309033</v>
       </c>
       <c r="X19" t="n">
-        <v>5116934.532715378</v>
+        <v>5292636.933904922</v>
       </c>
       <c r="Y19" t="n">
-        <v>74158.47148862867</v>
+        <v>76704.88310007133</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ19" t="n">
-        <v>5014595.842061071</v>
+        <v>5186784.195226823</v>
       </c>
       <c r="AK19" t="n">
-        <v>72675.30205885609</v>
+        <v>75170.7854380699</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         <v>67724.17828091094</v>
       </c>
       <c r="R20" t="n">
-        <v>8920643.958117928</v>
+        <v>10025863.13144666</v>
       </c>
       <c r="S20" t="n">
-        <v>80293.82500556191</v>
+        <v>90241.79236225614</v>
       </c>
       <c r="T20" t="n">
         <v>0.7</v>
@@ -2962,13 +2962,13 @@
         <v>5266909.344906443</v>
       </c>
       <c r="W20" t="n">
-        <v>2676193.187435378</v>
+        <v>3007758.939433997</v>
       </c>
       <c r="X20" t="n">
-        <v>7943102.532341821</v>
+        <v>8274668.284340439</v>
       </c>
       <c r="Y20" t="n">
-        <v>71495.07229830623</v>
+        <v>74479.46250531448</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7784240.481694984</v>
+        <v>8109174.918653631</v>
       </c>
       <c r="AK20" t="n">
-        <v>70065.1708523401</v>
+        <v>72989.87325520821</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
         <v>72544.49730384856</v>
       </c>
       <c r="R21" t="n">
-        <v>5668450.312948689</v>
+        <v>6256329.670858588</v>
       </c>
       <c r="S21" t="n">
-        <v>82151.45381085057</v>
+        <v>90671.44450519692</v>
       </c>
       <c r="T21" t="n">
         <v>0.7</v>
@@ -3090,13 +3090,13 @@
         <v>3503899.219775885</v>
       </c>
       <c r="W21" t="n">
-        <v>1700535.093884607</v>
+        <v>1876898.901257576</v>
       </c>
       <c r="X21" t="n">
-        <v>5204434.313660492</v>
+        <v>5380798.121033462</v>
       </c>
       <c r="Y21" t="n">
-        <v>75426.58425594916</v>
+        <v>77982.58146425307</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5100345.627387282</v>
+        <v>5273182.158612792</v>
       </c>
       <c r="AK21" t="n">
-        <v>73918.05257083019</v>
+        <v>76422.929834968</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         <v>72544.49730384856</v>
       </c>
       <c r="R22" t="n">
-        <v>5696976.638043852</v>
+        <v>6166963.902386568</v>
       </c>
       <c r="S22" t="n">
-        <v>82564.87881222973</v>
+        <v>89376.28844038503</v>
       </c>
       <c r="T22" t="n">
         <v>0.7</v>
@@ -3214,13 +3214,13 @@
         <v>3503899.219775885</v>
       </c>
       <c r="W22" t="n">
-        <v>1709092.991413155</v>
+        <v>1850089.17071597</v>
       </c>
       <c r="X22" t="n">
-        <v>5212992.211189041</v>
+        <v>5353988.390491855</v>
       </c>
       <c r="Y22" t="n">
-        <v>75550.61175636291</v>
+        <v>77594.03464480949</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5108732.36696526</v>
+        <v>5246908.622682018</v>
       </c>
       <c r="AK22" t="n">
-        <v>74039.59952123565</v>
+        <v>76042.15395191331</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
         <v>72544.49730384856</v>
       </c>
       <c r="R23" t="n">
-        <v>5668362.861734515</v>
+        <v>6047833.01271629</v>
       </c>
       <c r="S23" t="n">
-        <v>82150.1864019495</v>
+        <v>87649.75380748246</v>
       </c>
       <c r="T23" t="n">
         <v>0.7</v>
@@ -3342,13 +3342,13 @@
         <v>3503899.219775885</v>
       </c>
       <c r="W23" t="n">
-        <v>1700508.858520354</v>
+        <v>1814349.903814887</v>
       </c>
       <c r="X23" t="n">
-        <v>5204408.078296239</v>
+        <v>5318249.123590772</v>
       </c>
       <c r="Y23" t="n">
-        <v>75426.20403327883</v>
+        <v>77076.07425493872</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5100319.916730314</v>
+        <v>5211884.141118957</v>
       </c>
       <c r="AK23" t="n">
-        <v>73917.67995261325</v>
+        <v>75534.55276983995</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         <v>69227.27882046724</v>
       </c>
       <c r="R24" t="n">
-        <v>8872199.298084021</v>
+        <v>9588937.711060483</v>
       </c>
       <c r="S24" t="n">
-        <v>79857.77946070227</v>
+        <v>86309.07030657501</v>
       </c>
       <c r="T24" t="n">
         <v>0.7</v>
@@ -3470,13 +3470,13 @@
         <v>5383805.473867737</v>
       </c>
       <c r="W24" t="n">
-        <v>2661659.789425206</v>
+        <v>2876681.313318145</v>
       </c>
       <c r="X24" t="n">
-        <v>8045465.263292942</v>
+        <v>8260486.787185881</v>
       </c>
       <c r="Y24" t="n">
-        <v>72416.42901253773</v>
+        <v>74351.81626629956</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7884555.958027083</v>
+        <v>8095277.051442163</v>
       </c>
       <c r="AK24" t="n">
-        <v>70968.10043228698</v>
+        <v>72864.77994097357</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -3583,10 +3583,10 @@
         <v>74964.70701319211</v>
       </c>
       <c r="R25" t="n">
-        <v>5700494.331486938</v>
+        <v>6117598.831653668</v>
       </c>
       <c r="S25" t="n">
-        <v>82615.85987662229</v>
+        <v>88660.85263266184</v>
       </c>
       <c r="T25" t="n">
         <v>0.7</v>
@@ -3598,13 +3598,13 @@
         <v>3620795.348737178</v>
       </c>
       <c r="W25" t="n">
-        <v>1710148.299446081</v>
+        <v>1835279.6494961</v>
       </c>
       <c r="X25" t="n">
-        <v>5330943.64818326</v>
+        <v>5456074.998233278</v>
       </c>
       <c r="Y25" t="n">
-        <v>77260.05287222116</v>
+        <v>79073.55069903302</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5224324.775219595</v>
+        <v>5346953.498268613</v>
       </c>
       <c r="AK25" t="n">
-        <v>75714.85181477675</v>
+        <v>77492.07968505236</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
         <v>74964.70701319211</v>
       </c>
       <c r="R26" t="n">
-        <v>5826100.650722891</v>
+        <v>6419820.758222252</v>
       </c>
       <c r="S26" t="n">
-        <v>84436.24131482451</v>
+        <v>93040.88055394568</v>
       </c>
       <c r="T26" t="n">
         <v>0.7</v>
@@ -3722,13 +3722,13 @@
         <v>3620795.348737178</v>
       </c>
       <c r="W26" t="n">
-        <v>1747830.195216867</v>
+        <v>1925946.227466675</v>
       </c>
       <c r="X26" t="n">
-        <v>5368625.543954046</v>
+        <v>5546741.576203854</v>
       </c>
       <c r="Y26" t="n">
-        <v>77806.16730368182</v>
+        <v>80387.55907541818</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ26" t="n">
-        <v>5261253.033074965</v>
+        <v>5435806.744679777</v>
       </c>
       <c r="AK26" t="n">
-        <v>76250.04395760818</v>
+        <v>78779.8078939098</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
         <v>74964.70701319211</v>
       </c>
       <c r="R27" t="n">
-        <v>5802185.152644323</v>
+        <v>6408213.654358612</v>
       </c>
       <c r="S27" t="n">
-        <v>84089.63989339599</v>
+        <v>92872.66165737119</v>
       </c>
       <c r="T27" t="n">
         <v>0.7</v>
@@ -3850,13 +3850,13 @@
         <v>3620795.348737178</v>
       </c>
       <c r="W27" t="n">
-        <v>1740655.545793297</v>
+        <v>1922464.096307584</v>
       </c>
       <c r="X27" t="n">
-        <v>5361450.894530475</v>
+        <v>5543259.445044762</v>
       </c>
       <c r="Y27" t="n">
-        <v>77702.18687725326</v>
+        <v>80337.09340644581</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3893,10 +3893,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5254221.876639865</v>
+        <v>5432394.256143866</v>
       </c>
       <c r="AK27" t="n">
-        <v>76148.14313970819</v>
+        <v>78730.3515383169</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         <v>70730.37936002354</v>
       </c>
       <c r="R28" t="n">
-        <v>8956390.971092965</v>
+        <v>10081963.97550417</v>
       </c>
       <c r="S28" t="n">
-        <v>80615.58029786649</v>
+        <v>90746.750454583</v>
       </c>
       <c r="T28" t="n">
         <v>0.7</v>
@@ -3978,13 +3978,13 @@
         <v>5500701.60282903</v>
       </c>
       <c r="W28" t="n">
-        <v>2686917.29132789</v>
+        <v>3024589.192651251</v>
       </c>
       <c r="X28" t="n">
-        <v>8187618.89415692</v>
+        <v>8525290.795480281</v>
       </c>
       <c r="Y28" t="n">
-        <v>73695.93964137642</v>
+        <v>76735.29068839137</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8023866.516273782</v>
+        <v>8354784.979570676</v>
       </c>
       <c r="AK28" t="n">
-        <v>72222.0208485489</v>
+        <v>75200.58487462354</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         <v>77384.91672253564</v>
       </c>
       <c r="R29" t="n">
-        <v>5704197.325923725</v>
+        <v>6312430.514916101</v>
       </c>
       <c r="S29" t="n">
-        <v>82669.52646266269</v>
+        <v>91484.50021617538</v>
       </c>
       <c r="T29" t="n">
         <v>0.7</v>
@@ -4102,13 +4102,13 @@
         <v>3737691.477698471</v>
       </c>
       <c r="W29" t="n">
-        <v>1711259.197777117</v>
+        <v>1893729.15447483</v>
       </c>
       <c r="X29" t="n">
-        <v>5448950.675475589</v>
+        <v>5631420.632173302</v>
       </c>
       <c r="Y29" t="n">
-        <v>78970.29964457375</v>
+        <v>81614.79177062756</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ29" t="n">
-        <v>5339971.661966077</v>
+        <v>5518792.219529836</v>
       </c>
       <c r="AK29" t="n">
-        <v>77390.89365168227</v>
+        <v>79982.495935215</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -4211,10 +4211,10 @@
         <v>77384.91672253564</v>
       </c>
       <c r="R30" t="n">
-        <v>5732723.651018888</v>
+        <v>6223064.746444081</v>
       </c>
       <c r="S30" t="n">
-        <v>83082.95146404185</v>
+        <v>90189.34415136349</v>
       </c>
       <c r="T30" t="n">
         <v>0.7</v>
@@ -4226,13 +4226,13 @@
         <v>3737691.477698471</v>
       </c>
       <c r="W30" t="n">
-        <v>1719817.095305666</v>
+        <v>1866919.423933224</v>
       </c>
       <c r="X30" t="n">
-        <v>5457508.573004138</v>
+        <v>5604610.901631696</v>
       </c>
       <c r="Y30" t="n">
-        <v>79094.3271449875</v>
+        <v>81226.24495118399</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ30" t="n">
-        <v>5348358.401544055</v>
+        <v>5492518.683599062</v>
       </c>
       <c r="AK30" t="n">
-        <v>77512.44060208775</v>
+        <v>79601.72005216032</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -4339,10 +4339,10 @@
         <v>77384.91672253564</v>
       </c>
       <c r="R31" t="n">
-        <v>5704109.874709551</v>
+        <v>6103933.856773803</v>
       </c>
       <c r="S31" t="n">
-        <v>82668.25905376161</v>
+        <v>88462.80951846091</v>
       </c>
       <c r="T31" t="n">
         <v>0.7</v>
@@ -4354,13 +4354,13 @@
         <v>3737691.477698471</v>
       </c>
       <c r="W31" t="n">
-        <v>1711232.962412865</v>
+        <v>1831180.157032141</v>
       </c>
       <c r="X31" t="n">
-        <v>5448924.440111337</v>
+        <v>5568871.634730612</v>
       </c>
       <c r="Y31" t="n">
-        <v>78969.91942190344</v>
+        <v>80708.28456131322</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -4397,10 +4397,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5339945.95130911</v>
+        <v>5457494.202036</v>
       </c>
       <c r="AK31" t="n">
-        <v>77390.52103346537</v>
+        <v>79094.11887008695</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         <v>72233.47989957983</v>
       </c>
       <c r="R32" t="n">
-        <v>8907946.311059056</v>
+        <v>9645038.555117995</v>
       </c>
       <c r="S32" t="n">
-        <v>80179.53475300681</v>
+        <v>86814.02839890185</v>
       </c>
       <c r="T32" t="n">
         <v>0.7</v>
@@ -4482,13 +4482,13 @@
         <v>5617597.731790323</v>
       </c>
       <c r="W32" t="n">
-        <v>2672383.893317717</v>
+        <v>2893511.566535398</v>
       </c>
       <c r="X32" t="n">
-        <v>8289981.625108039</v>
+        <v>8511109.298325721</v>
       </c>
       <c r="Y32" t="n">
-        <v>74617.29635560792</v>
+        <v>76607.64444937643</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ32" t="n">
-        <v>8124181.992605878</v>
+        <v>8340887.112359206</v>
       </c>
       <c r="AK32" t="n">
-        <v>73124.95042849575</v>
+        <v>75075.49156038889</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -4591,10 +4591,10 @@
         <v>79805.12643187919</v>
       </c>
       <c r="R33" t="n">
-        <v>5736241.344461974</v>
+        <v>6173699.675711181</v>
       </c>
       <c r="S33" t="n">
-        <v>83133.93252843441</v>
+        <v>89473.9083436403</v>
       </c>
       <c r="T33" t="n">
         <v>0.7</v>
@@ -4606,13 +4606,13 @@
         <v>3854587.606659765</v>
       </c>
       <c r="W33" t="n">
-        <v>1720872.403338592</v>
+        <v>1852109.902713354</v>
       </c>
       <c r="X33" t="n">
-        <v>5575460.009998357</v>
+        <v>5706697.509373119</v>
       </c>
       <c r="Y33" t="n">
-        <v>80803.76826084575</v>
+        <v>82705.76100540752</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -4649,10 +4649,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ33" t="n">
-        <v>5463950.80979839</v>
+        <v>5592563.559185657</v>
       </c>
       <c r="AK33" t="n">
-        <v>79187.69289562883</v>
+        <v>81051.64578529938</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
         <v>79805.12643187919</v>
       </c>
       <c r="R34" t="n">
-        <v>5861847.663697927</v>
+        <v>6475921.602279765</v>
       </c>
       <c r="S34" t="n">
-        <v>84954.31396663663</v>
+        <v>93853.93626492412</v>
       </c>
       <c r="T34" t="n">
         <v>0.7</v>
@@ -4730,13 +4730,13 @@
         <v>3854587.606659765</v>
       </c>
       <c r="W34" t="n">
-        <v>1758554.299109378</v>
+        <v>1942776.480683929</v>
       </c>
       <c r="X34" t="n">
-        <v>5613141.905769143</v>
+        <v>5797364.087343695</v>
       </c>
       <c r="Y34" t="n">
-        <v>81349.88269230642</v>
+        <v>84019.76938179268</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ34" t="n">
-        <v>5500879.06765376</v>
+        <v>5681416.805596821</v>
       </c>
       <c r="AK34" t="n">
-        <v>79722.8850384603</v>
+        <v>82339.37399415682</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
         <v>79805.12643187919</v>
       </c>
       <c r="R35" t="n">
-        <v>5837932.165619359</v>
+        <v>6464314.498416126</v>
       </c>
       <c r="S35" t="n">
-        <v>84607.71254520811</v>
+        <v>93685.71736834965</v>
       </c>
       <c r="T35" t="n">
         <v>0.7</v>
@@ -4854,13 +4854,13 @@
         <v>3854587.606659765</v>
       </c>
       <c r="W35" t="n">
-        <v>1751379.649685808</v>
+        <v>1939294.349524838</v>
       </c>
       <c r="X35" t="n">
-        <v>5605967.256345573</v>
+        <v>5793881.956184602</v>
       </c>
       <c r="Y35" t="n">
-        <v>81245.90226587787</v>
+        <v>83969.30371282033</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5493847.911218661</v>
+        <v>5678004.31706091</v>
       </c>
       <c r="AK35" t="n">
-        <v>79620.98422056031</v>
+        <v>82289.91763856391</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
         <v>73736.58043913613</v>
       </c>
       <c r="R36" t="n">
-        <v>8992137.984068001</v>
+        <v>10138064.81956168</v>
       </c>
       <c r="S36" t="n">
-        <v>80937.33559017103</v>
+        <v>91251.70854690984</v>
       </c>
       <c r="T36" t="n">
         <v>0.7</v>
@@ -4982,13 +4982,13 @@
         <v>5734493.860751617</v>
       </c>
       <c r="W36" t="n">
-        <v>2697641.3952204</v>
+        <v>3041419.445868505</v>
       </c>
       <c r="X36" t="n">
-        <v>8432135.255972017</v>
+        <v>8775913.306620121</v>
       </c>
       <c r="Y36" t="n">
-        <v>75896.80698444659</v>
+        <v>78991.11887146824</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -5025,10 +5025,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ36" t="n">
-        <v>8263492.550852576</v>
+        <v>8600395.040487718</v>
       </c>
       <c r="AK36" t="n">
-        <v>74378.87084475766</v>
+        <v>77411.29649403886</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -5095,10 +5095,10 @@
         <v>68265.53503471646</v>
       </c>
       <c r="R37" t="n">
-        <v>21706658.10427722</v>
+        <v>23716211.17771592</v>
       </c>
       <c r="S37" t="n">
-        <v>85057.43771268504</v>
+        <v>92931.86198164547</v>
       </c>
       <c r="T37" t="n">
         <v>0.7</v>
@@ -5110,13 +5110,13 @@
         <v>12194955.17860175</v>
       </c>
       <c r="W37" t="n">
-        <v>6511997.431283167</v>
+        <v>7114863.353314777</v>
       </c>
       <c r="X37" t="n">
-        <v>18706952.60988491</v>
+        <v>19309818.53191653</v>
       </c>
       <c r="Y37" t="n">
-        <v>73303.10583810703</v>
+        <v>75665.43311879516</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ37" t="n">
-        <v>18332813.55768722</v>
+        <v>18923622.1612782</v>
       </c>
       <c r="AK37" t="n">
-        <v>71837.04372134489</v>
+        <v>74152.12445641926</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -5223,10 +5223,10 @@
         <v>68161.33110388041</v>
       </c>
       <c r="R38" t="n">
-        <v>22152250.92142075</v>
+        <v>24062814.02693537</v>
       </c>
       <c r="S38" t="n">
-        <v>85168.20807928006</v>
+        <v>92513.70252570308</v>
       </c>
       <c r="T38" t="n">
         <v>0.7</v>
@@ -5238,13 +5238,13 @@
         <v>12410133.55408351</v>
       </c>
       <c r="W38" t="n">
-        <v>6645675.276426223</v>
+        <v>7218844.208080611</v>
       </c>
       <c r="X38" t="n">
-        <v>19055808.83050973</v>
+        <v>19628977.76216412</v>
       </c>
       <c r="Y38" t="n">
-        <v>73263.3941965003</v>
+        <v>75467.04253042721</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ38" t="n">
-        <v>18674692.65389954</v>
+        <v>19236398.20692084</v>
       </c>
       <c r="AK38" t="n">
-        <v>71798.1263125703</v>
+        <v>73957.70167981867</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -5351,10 +5351,10 @@
         <v>71163.53463883368</v>
       </c>
       <c r="R39" t="n">
-        <v>14046046.54011757</v>
+        <v>15015372.50264205</v>
       </c>
       <c r="S39" t="n">
-        <v>82575.22951274294</v>
+        <v>88273.79484210492</v>
       </c>
       <c r="T39" t="n">
         <v>0.7</v>
@@ -5366,13 +5366,13 @@
         <v>8473442.069445925</v>
       </c>
       <c r="W39" t="n">
-        <v>4213813.962035271</v>
+        <v>4504611.750792614</v>
       </c>
       <c r="X39" t="n">
-        <v>12687256.0314812</v>
+        <v>12978053.82023854</v>
       </c>
       <c r="Y39" t="n">
-        <v>74587.04310100643</v>
+        <v>76296.61269981504</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ39" t="n">
-        <v>12433510.91085157</v>
+        <v>12718492.74383377</v>
       </c>
       <c r="AK39" t="n">
-        <v>73095.30223898632</v>
+        <v>74770.68044581874</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
         <v>71494.35068690831</v>
       </c>
       <c r="R40" t="n">
-        <v>13296305.5468278</v>
+        <v>13933792.47523753</v>
       </c>
       <c r="S40" t="n">
-        <v>83835.47003044009</v>
+        <v>87854.93363958089</v>
       </c>
       <c r="T40" t="n">
         <v>0.7</v>
@@ -5490,13 +5490,13 @@
         <v>7937302.813260559</v>
       </c>
       <c r="W40" t="n">
-        <v>3988891.664048339</v>
+        <v>4180137.742571259</v>
       </c>
       <c r="X40" t="n">
-        <v>11926194.4773089</v>
+        <v>12117440.55583182</v>
       </c>
       <c r="Y40" t="n">
-        <v>75196.68648996785</v>
+        <v>76402.52557271007</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
         <v>-0.02</v>
       </c>
       <c r="AJ40" t="n">
-        <v>11687670.58776272</v>
+        <v>11875091.74471518</v>
       </c>
       <c r="AK40" t="n">
-        <v>73692.75276016849</v>
+        <v>74874.47506125589</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
